--- a/storage/app/public/glosario.xlsx
+++ b/storage/app/public/glosario.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="512">
   <si>
     <t xml:space="preserve">utiliza_transporte</t>
   </si>
@@ -152,471 +152,477 @@
     <t xml:space="preserve">Encargado</t>
   </si>
   <si>
+    <t xml:space="preserve">Lunes y Martes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8:00 AM a 2:00 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T.S.U</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIGA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 Horas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fijo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extraviado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gerencia De Operaciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gcv Chile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claro Chile In</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bancamiga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMBOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">la california</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordinador De Operaciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Titular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martes y Miercoles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8:00 AM a 4:00 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boleita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contratado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emitido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claro Chile Out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BanCaribe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">los cortijos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Especialista de Bussiness Intelligence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miercoles y Jueves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8:00 AM a 5:00 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ING.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siemens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honorarios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claro Chile C2c Fijo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banco Activo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SI COLOCAS ESTE CAMPO CON LA OPCIÓN NO. EL HORARIO TRANSPORTE NO ES REQUERIDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">los dos caminos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lider Tec. Negocios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jueves y Viernes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9:00 AM a 3:00 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TECNICO MEDIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inter Sede</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finalizado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claro Chile - 103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banco Agrícola de Venezuela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">miranda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ejecutivo(a) de Negocios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viernes y Sabado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9:00 AM a 5:00 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAGISTER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HomeOffice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abandono</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claro Chile - Full Claro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banco Bicentenario del Pueblo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">altamira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formador(a)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sabado y Domingo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9:00 AM a 6:00 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macaracuay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pendiente Por Contrato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claro Chile - Pyme Movil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banco Caroní</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chacao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asistente Administrativo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:00 AM a 4:00 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTUDIANTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cantv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pendiente Por Documentacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claro Chile - Móvil Out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banco de Exportación y Comercio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chacaito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auxiliar De Limpieza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunes y Miercoles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:00 AM a 7:00 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBIIPAGOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingreso No Efectivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claro Chile - Fijo Out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banco de Venezuela (BDV)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sabana grande</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Operativo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunes y Jueves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:00 AM a 8:00 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claro Chile - Móvil In</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banco del Tesoro (BT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plaza venezuela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supervisor de Gestion Operativa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunes y Viernes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:00 AM a 9:00 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claro Chile - Fijo In</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banco Exterior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">colegio de ingenieros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supervisor Operativo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunes y Sabados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1:00 PM a 7:00 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claro Chile - Chat Movil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banco Internacional de Desarrollo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bellas artes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martes y Jueves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2:00 PM a 8:00 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claro Chile - Chat Fijo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banco Mercantil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parque carabobo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ejecutivo De ATC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martes y Viernes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:00 PM a 9:00 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claro Chile C2c Movil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banco Nacional de Crédito (BNC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">la hoyada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcionista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8:30 AM a 5:30 PM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claro Chile - Pyme Fijo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banco Plaza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">capitolio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Validador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martes y Sabado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claro Chile - Cross Fijo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banco Sofitasa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">caño amarillo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chofer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martes y Domingos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reactivofijo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banco Venezolano de Credito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agua salud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Community Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miercoles y Viernes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claro Ecuador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claro Ecuador Movil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bancrecer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gato negro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Success Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miercoles y Sabados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claro Ecuador Fijo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banesco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plaza sucre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Technical Support Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miercoles y Domingos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claro Ecuador Dth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BANFANB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">perez bonalde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diseñador Grafico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jueves y Sabados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claro Ecuador - B.o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bangente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">propatria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inside Sales</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jueves y Domingos</t>
   </si>
   <si>
-    <t xml:space="preserve">8:00 AM a 2:00 PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T.S.U</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Autana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIGA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 Horas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fijo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extraviado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gerencia De Operaciones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gcv Chile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claro Chile In</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bancamiga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMBOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">la california</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coordinador De Operaciones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Titular</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jueves y Sabados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8:00 AM a 4:00 PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boleita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contratado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emitido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claro Chile Out</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BanCaribe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">los cortijos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Especialista de Bussiness Intelligence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jueves y Viernes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8:00 AM a 5:00 PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ING.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siemens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Honorarios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claro Chile C2c Fijo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banco Activo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SI COLOCAS ESTE CAMPO CON LA OPCIÓN NO. EL HORARIO TRANSPORTE NO ES REQUERIDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">los dos caminos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lider Tec. Negocios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lunes y Jueves</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9:00 AM a 3:00 PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TECNICO MEDIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inter Sede</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finalizado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claro Chile - 103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banco Agrícola de Venezuela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">miranda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ejecutivo(a) de Negocios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lunes y Martes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9:00 AM a 5:00 PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAGISTER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HomeOffice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abandono</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claro Chile - Full Claro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banco Bicentenario del Pueblo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">altamira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formador(a)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lunes y Miercoles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9:00 AM a 6:00 PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OTRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Macaracuay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pendiente Por Contrato</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claro Chile - Pyme Movil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banco Caroní</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chacao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asistente Administrativo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lunes y Sabados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:00 AM a 4:00 PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESTUDIANTE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cantv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pendiente Por Documentacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claro Chile - Móvil Out</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banco de Exportación y Comercio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chacaito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auxiliar De Limpieza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lunes y Viernes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:00 AM a 7:00 PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingreso No Efectivo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claro Chile - Fijo Out</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banco de Venezuela (BDV)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sabana grande</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Operativo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martes y Domingos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:00 AM a 8:00 PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claro Chile - Móvil In</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banco del Tesoro (BT)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">plaza venezuela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supervisor de Gestion Operativa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martes y Jueves</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:00 AM a 9:00 PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claro Chile - Fijo In</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banco Exterior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">colegio de ingenieros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supervisor Operativo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martes y Miercoles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1:00 PM a 7:00 PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claro Chile - Chat Movil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banco Internacional de Desarrollo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bellas artes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analista</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martes y Sabado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2:00 PM a 8:00 PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claro Chile - Chat Fijo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banco Mercantil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">parque carabobo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ejecutivo De ATC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martes y Viernes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:00 PM a 9:00 PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claro Chile C2c Movil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banco Nacional de Crédito (BNC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">la hoyada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcionista</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miercoles y Domingos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claro Chile - Pyme Fijo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banco Plaza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">capitolio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miercoles y Jueves</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claro Chile - Cross Fijo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banco Sofitasa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">caño amarillo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chofer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miercoles y Sabados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reactivofijo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banco Venezolano de Credito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">agua salud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Community Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miercoles y Viernes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claro Ecuador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claro Ecuador Movil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bancrecer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gato negro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer Success Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sabado y Domingo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claro Ecuador Fijo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banesco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">plaza sucre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Customer Technical Support Manager</t>
+    <t xml:space="preserve">Claro Ecuador Móvil Prepago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banplus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">el silencio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lider Tecnico De Producto</t>
   </si>
   <si>
     <t xml:space="preserve">Viernes y Domingos</t>
   </si>
   <si>
-    <t xml:space="preserve">Claro Ecuador Dth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BANFANB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">perez bonalde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diseñador Grafico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viernes y Sabado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claro Ecuador - B.o</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bangente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">propatria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inside Sales</t>
+    <t xml:space="preserve">0800 Empresa - Inbound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BBVA Provincial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">capuchinos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Psicologo Organizacional</t>
   </si>
   <si>
     <t xml:space="preserve">Rotativo</t>
   </si>
   <si>
-    <t xml:space="preserve">Claro Ecuador Móvil Prepago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banplus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">el silencio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lider Tecnico De Producto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0800 Empresa - Inbound</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BBVA Provincial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">capuchinos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Psicologo Organizacional</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cobranzas Empresas</t>
   </si>
   <si>
@@ -1394,48 +1400,66 @@
     <t xml:space="preserve">Analista de Redes y Datos</t>
   </si>
   <si>
+    <t xml:space="preserve">Reina Ester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encuestas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asistente de Marca</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gerencia de Formacion y Calidad</t>
   </si>
   <si>
     <t xml:space="preserve">Formación</t>
   </si>
   <si>
-    <t xml:space="preserve">Asistente de Marca</t>
+    <t xml:space="preserve">Ejecutivo Comercial</t>
   </si>
   <si>
     <t xml:space="preserve">Calidad</t>
   </si>
   <si>
-    <t xml:space="preserve">Ejecutivo Comercial</t>
+    <t xml:space="preserve">Backoffice de Mercadeo</t>
   </si>
   <si>
     <t xml:space="preserve">Captación</t>
   </si>
   <si>
-    <t xml:space="preserve">Backoffice de Mercadeo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Asesor Comercial</t>
   </si>
   <si>
+    <t xml:space="preserve">Supervisor de Ventas</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gerencia Business Intelligence</t>
   </si>
   <si>
-    <t xml:space="preserve">Supervisor de Ventas</t>
-  </si>
-  <si>
     <t xml:space="preserve">Coordinadora de Captación y Selección de  Talentos</t>
   </si>
   <si>
+    <t xml:space="preserve">Coordinador de Mercadeo y RRPP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backoffice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backoficce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analista de Back Office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supervisor Senior de BackOffice</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gerencia De Tecnología</t>
   </si>
   <si>
-    <t xml:space="preserve">Coordinador de Mercadeo y RRPP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analista de Back Office</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dirección Comercial</t>
   </si>
   <si>
@@ -1467,6 +1491,72 @@
   </si>
   <si>
     <t xml:space="preserve">Administrativo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROT</t>
   </si>
 </sst>
 </file>
@@ -1544,7 +1634,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -1587,13 +1677,6 @@
       <bottom style="thin"/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1620,7 +1703,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1670,7 +1753,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1701,16 +1784,8 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1904,7 +1979,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AM141"/>
+  <dimension ref="A1:AM145"/>
   <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.67"/>
@@ -2050,10 +2125,10 @@
       </c>
       <c r="N2" s="10"/>
       <c r="O2" s="12" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P2" s="10"/>
-      <c r="Q2" s="8" t="s">
+      <c r="Q2" s="1" t="s">
         <v>26</v>
       </c>
       <c r="R2" s="9"/>
@@ -2122,10 +2197,10 @@
       </c>
       <c r="N3" s="10"/>
       <c r="O3" s="11" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="P3" s="10"/>
-      <c r="Q3" s="8" t="s">
+      <c r="Q3" s="1" t="s">
         <v>43</v>
       </c>
       <c r="R3" s="9"/>
@@ -2184,10 +2259,10 @@
       <c r="M4" s="17"/>
       <c r="N4" s="10"/>
       <c r="O4" s="11" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="P4" s="10"/>
-      <c r="Q4" s="8" t="s">
+      <c r="Q4" s="1" t="s">
         <v>59</v>
       </c>
       <c r="R4" s="9"/>
@@ -2238,10 +2313,10 @@
       <c r="M5" s="17"/>
       <c r="N5" s="10"/>
       <c r="O5" s="11" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="P5" s="10"/>
-      <c r="Q5" s="8" t="s">
+      <c r="Q5" s="1" t="s">
         <v>70</v>
       </c>
       <c r="R5" s="9"/>
@@ -2288,11 +2363,11 @@
       <c r="L6" s="10"/>
       <c r="M6" s="17"/>
       <c r="N6" s="10"/>
-      <c r="O6" s="20" t="n">
-        <v>270</v>
+      <c r="O6" s="11" t="n">
+        <v>150</v>
       </c>
       <c r="P6" s="10"/>
-      <c r="Q6" s="8" t="s">
+      <c r="Q6" s="1" t="s">
         <v>80</v>
       </c>
       <c r="R6" s="9"/>
@@ -2337,9 +2412,11 @@
       <c r="L7" s="10"/>
       <c r="M7" s="17"/>
       <c r="N7" s="10"/>
-      <c r="O7" s="17"/>
+      <c r="O7" s="11" t="n">
+        <v>180</v>
+      </c>
       <c r="P7" s="10"/>
-      <c r="Q7" s="8" t="s">
+      <c r="Q7" s="1" t="s">
         <v>89</v>
       </c>
       <c r="R7" s="9"/>
@@ -2384,9 +2461,11 @@
       <c r="L8" s="10"/>
       <c r="M8" s="17"/>
       <c r="N8" s="10"/>
-      <c r="O8" s="17"/>
+      <c r="O8" s="11" t="n">
+        <v>210</v>
+      </c>
       <c r="P8" s="10"/>
-      <c r="Q8" s="8" t="s">
+      <c r="Q8" s="1" t="s">
         <v>98</v>
       </c>
       <c r="R8" s="9"/>
@@ -2431,24 +2510,26 @@
       <c r="L9" s="10"/>
       <c r="M9" s="17"/>
       <c r="N9" s="10"/>
-      <c r="O9" s="17"/>
+      <c r="O9" s="11" t="n">
+        <v>240</v>
+      </c>
       <c r="P9" s="10"/>
-      <c r="Q9" s="8" t="s">
-        <v>107</v>
+      <c r="Q9" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="R9" s="9"/>
       <c r="S9" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="T9" s="9"/>
+      <c r="U9" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="T9" s="9"/>
-      <c r="U9" s="21" t="s">
+      <c r="W9" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="W9" s="21" t="s">
+      <c r="AC9" s="16" t="s">
         <v>110</v>
-      </c>
-      <c r="AC9" s="16" t="s">
-        <v>111</v>
       </c>
       <c r="AI9" s="15" t="s">
         <v>51</v>
@@ -2457,19 +2538,19 @@
         <v>52</v>
       </c>
       <c r="AK9" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="AM9" s="8" t="s">
         <v>112</v>
-      </c>
-      <c r="AM9" s="8" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="19"/>
       <c r="E10" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="H10" s="10"/>
       <c r="I10" s="17"/>
@@ -2478,18 +2559,22 @@
       <c r="L10" s="10"/>
       <c r="M10" s="17"/>
       <c r="N10" s="10"/>
-      <c r="O10" s="17"/>
+      <c r="O10" s="11" t="n">
+        <v>270</v>
+      </c>
       <c r="P10" s="10"/>
-      <c r="Q10" s="8" t="s">
-        <v>116</v>
+      <c r="Q10" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="R10" s="9"/>
       <c r="S10" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="T10" s="9"/>
       <c r="U10" s="8"/>
-      <c r="W10" s="8"/>
+      <c r="W10" s="8" t="s">
+        <v>117</v>
+      </c>
       <c r="AC10" s="1" t="s">
         <v>118</v>
       </c>
@@ -2521,15 +2606,16 @@
       <c r="L11" s="10"/>
       <c r="M11" s="17"/>
       <c r="N11" s="10"/>
-      <c r="O11" s="17"/>
+      <c r="O11" s="11"/>
       <c r="P11" s="10"/>
-      <c r="Q11" s="8" t="s">
+      <c r="Q11" s="1" t="s">
         <v>123</v>
       </c>
       <c r="S11" s="13" t="s">
         <v>124</v>
       </c>
       <c r="U11" s="8"/>
+      <c r="W11" s="8"/>
       <c r="AI11" s="15" t="s">
         <v>51</v>
       </c>
@@ -2560,7 +2646,7 @@
       <c r="N12" s="10"/>
       <c r="O12" s="17"/>
       <c r="P12" s="10"/>
-      <c r="Q12" s="8" t="s">
+      <c r="Q12" s="1" t="s">
         <v>129</v>
       </c>
       <c r="S12" s="13" t="s">
@@ -2597,7 +2683,7 @@
       <c r="N13" s="10"/>
       <c r="O13" s="17"/>
       <c r="P13" s="10"/>
-      <c r="Q13" s="8" t="s">
+      <c r="Q13" s="1" t="s">
         <v>135</v>
       </c>
       <c r="S13" s="13" t="s">
@@ -2632,7 +2718,7 @@
       <c r="N14" s="10"/>
       <c r="O14" s="17"/>
       <c r="P14" s="10"/>
-      <c r="Q14" s="8" t="s">
+      <c r="Q14" s="1" t="s">
         <v>141</v>
       </c>
       <c r="S14" s="13" t="s">
@@ -2667,10 +2753,10 @@
       <c r="N15" s="10"/>
       <c r="O15" s="17"/>
       <c r="P15" s="10"/>
-      <c r="Q15" s="8" t="s">
+      <c r="Q15" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="S15" s="22" t="s">
+      <c r="S15" s="1" t="s">
         <v>148</v>
       </c>
       <c r="AI15" s="15" t="s">
@@ -2702,7 +2788,10 @@
       <c r="N16" s="10"/>
       <c r="O16" s="17"/>
       <c r="P16" s="10"/>
-      <c r="Q16" s="8" t="s">
+      <c r="Q16" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="S16" s="1" t="s">
         <v>153</v>
       </c>
       <c r="AI16" s="15" t="s">
@@ -2734,7 +2823,7 @@
       <c r="N17" s="10"/>
       <c r="O17" s="17"/>
       <c r="P17" s="10"/>
-      <c r="Q17" s="8" t="s">
+      <c r="Q17" s="1" t="s">
         <v>158</v>
       </c>
       <c r="AI17" s="15" t="s">
@@ -2766,7 +2855,7 @@
       <c r="N18" s="10"/>
       <c r="O18" s="17"/>
       <c r="P18" s="10"/>
-      <c r="Q18" s="8" t="s">
+      <c r="Q18" s="1" t="s">
         <v>163</v>
       </c>
       <c r="AI18" s="15" t="s">
@@ -2798,7 +2887,7 @@
       <c r="N19" s="10"/>
       <c r="O19" s="17"/>
       <c r="P19" s="10"/>
-      <c r="Q19" s="8" t="s">
+      <c r="Q19" s="1" t="s">
         <v>168</v>
       </c>
       <c r="AI19" s="15" t="s">
@@ -2830,7 +2919,7 @@
       <c r="N20" s="10"/>
       <c r="O20" s="17"/>
       <c r="P20" s="10"/>
-      <c r="Q20" s="8" t="s">
+      <c r="Q20" s="1" t="s">
         <v>174</v>
       </c>
       <c r="AI20" s="15" t="s">
@@ -2862,7 +2951,7 @@
       <c r="N21" s="10"/>
       <c r="O21" s="17"/>
       <c r="P21" s="10"/>
-      <c r="Q21" s="8" t="s">
+      <c r="Q21" s="1" t="s">
         <v>179</v>
       </c>
       <c r="AI21" s="15" t="s">
@@ -2894,7 +2983,7 @@
       <c r="N22" s="10"/>
       <c r="O22" s="17"/>
       <c r="P22" s="10"/>
-      <c r="Q22" s="17" t="s">
+      <c r="Q22" s="1" t="s">
         <v>184</v>
       </c>
       <c r="AI22" s="15" t="s">
@@ -2958,50 +3047,56 @@
       <c r="N24" s="10"/>
       <c r="O24" s="17"/>
       <c r="P24" s="10"/>
+      <c r="Q24" s="1" t="s">
+        <v>194</v>
+      </c>
       <c r="AI24" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ24" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AK24" s="15" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AM24" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E25" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H25" s="10"/>
       <c r="I25" s="17"/>
       <c r="K25" s="17"/>
       <c r="M25" s="17"/>
       <c r="O25" s="17"/>
+      <c r="Q25" s="1" t="s">
+        <v>199</v>
+      </c>
       <c r="AI25" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ25" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AK25" s="15" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AM25" s="8" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E26" s="8" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H26" s="10"/>
       <c r="I26" s="17"/>
@@ -3012,21 +3107,21 @@
         <v>51</v>
       </c>
       <c r="AJ26" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AK26" s="15" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AM26" s="8" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E27" s="8" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H27" s="10"/>
       <c r="I27" s="17"/>
@@ -3037,21 +3132,21 @@
         <v>51</v>
       </c>
       <c r="AJ27" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AK27" s="15" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AM27" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E28" s="8" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H28" s="10"/>
       <c r="I28" s="17"/>
@@ -3059,27 +3154,27 @@
       <c r="M28" s="17"/>
       <c r="O28" s="17"/>
       <c r="Z28" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AI28" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ28" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AK28" s="15" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AM28" s="8" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E29" s="8" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H29" s="10"/>
       <c r="I29" s="17"/>
@@ -3090,21 +3185,21 @@
         <v>51</v>
       </c>
       <c r="AJ29" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AK29" s="15" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AM29" s="8" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E30" s="8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H30" s="10"/>
       <c r="I30" s="17"/>
@@ -3115,21 +3210,21 @@
         <v>51</v>
       </c>
       <c r="AJ30" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AK30" s="15" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AM30" s="16" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E31" s="8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H31" s="10"/>
       <c r="I31" s="17"/>
@@ -3140,18 +3235,18 @@
         <v>51</v>
       </c>
       <c r="AJ31" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AK31" s="15" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E32" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H32" s="10"/>
       <c r="I32" s="17"/>
@@ -3162,18 +3257,18 @@
         <v>51</v>
       </c>
       <c r="AJ32" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AK32" s="15" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E33" s="8" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H33" s="10"/>
       <c r="I33" s="17"/>
@@ -3184,18 +3279,18 @@
         <v>51</v>
       </c>
       <c r="AJ33" s="15" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AK33" s="15" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E34" s="8" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H34" s="10"/>
       <c r="I34" s="17"/>
@@ -3206,18 +3301,18 @@
         <v>51</v>
       </c>
       <c r="AJ34" s="15" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AK34" s="15" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E35" s="8" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H35" s="10"/>
       <c r="I35" s="17"/>
@@ -3228,18 +3323,18 @@
         <v>51</v>
       </c>
       <c r="AJ35" s="15" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AK35" s="15" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E36" s="8" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="H36" s="10"/>
       <c r="I36" s="17"/>
@@ -3250,18 +3345,18 @@
         <v>51</v>
       </c>
       <c r="AJ36" s="15" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AK36" s="15" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E37" s="8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="H37" s="10"/>
       <c r="I37" s="17"/>
@@ -3272,18 +3367,18 @@
         <v>51</v>
       </c>
       <c r="AJ37" s="15" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AK37" s="15" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E38" s="8" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="H38" s="10"/>
       <c r="I38" s="17"/>
@@ -3294,18 +3389,18 @@
         <v>51</v>
       </c>
       <c r="AJ38" s="15" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AK38" s="15" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E39" s="8" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="H39" s="10"/>
       <c r="I39" s="17"/>
@@ -3316,1746 +3411,1749 @@
         <v>51</v>
       </c>
       <c r="AJ39" s="15" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AK39" s="15" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E40" s="8" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H40" s="10"/>
       <c r="I40" s="17"/>
       <c r="K40" s="17"/>
       <c r="M40" s="17"/>
       <c r="O40" s="17"/>
-      <c r="U40" s="23"/>
+      <c r="U40" s="21"/>
       <c r="AI40" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ40" s="15" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AK40" s="15" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E41" s="8" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H41" s="10"/>
       <c r="I41" s="17"/>
       <c r="K41" s="17"/>
       <c r="M41" s="17"/>
       <c r="O41" s="17"/>
-      <c r="S41" s="23"/>
-      <c r="U41" s="23"/>
+      <c r="S41" s="21"/>
+      <c r="U41" s="21"/>
       <c r="AI41" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ41" s="15" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AK41" s="15" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E42" s="8" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="H42" s="10"/>
       <c r="I42" s="17"/>
       <c r="K42" s="17"/>
       <c r="M42" s="17"/>
       <c r="O42" s="17"/>
-      <c r="S42" s="23"/>
-      <c r="U42" s="23"/>
+      <c r="S42" s="21"/>
+      <c r="U42" s="21"/>
       <c r="AI42" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ42" s="15" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AK42" s="15" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E43" s="8" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H43" s="10"/>
       <c r="I43" s="17"/>
       <c r="K43" s="17"/>
       <c r="M43" s="17"/>
       <c r="O43" s="17"/>
-      <c r="S43" s="23"/>
-      <c r="U43" s="23"/>
+      <c r="S43" s="21"/>
+      <c r="U43" s="21"/>
       <c r="AI43" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ43" s="15" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AK43" s="15" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E44" s="8" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H44" s="10"/>
       <c r="I44" s="17"/>
       <c r="K44" s="17"/>
       <c r="M44" s="17"/>
       <c r="O44" s="17"/>
-      <c r="S44" s="23"/>
-      <c r="U44" s="23"/>
+      <c r="S44" s="21"/>
+      <c r="U44" s="21"/>
       <c r="AI44" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ44" s="15" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AK44" s="15" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E45" s="8" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H45" s="10"/>
       <c r="I45" s="17"/>
       <c r="K45" s="17"/>
       <c r="M45" s="17"/>
       <c r="O45" s="17"/>
-      <c r="S45" s="23"/>
-      <c r="U45" s="23"/>
+      <c r="S45" s="21"/>
+      <c r="U45" s="21"/>
       <c r="AI45" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ45" s="15" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AK45" s="15" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E46" s="8" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="H46" s="10"/>
       <c r="I46" s="17"/>
       <c r="K46" s="17"/>
       <c r="M46" s="17"/>
       <c r="O46" s="17"/>
-      <c r="S46" s="23"/>
-      <c r="U46" s="23"/>
+      <c r="S46" s="21"/>
+      <c r="U46" s="21"/>
       <c r="AI46" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ46" s="15" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AK46" s="15" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E47" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="H47" s="10"/>
       <c r="I47" s="17"/>
       <c r="K47" s="17"/>
       <c r="M47" s="17"/>
       <c r="O47" s="17"/>
-      <c r="S47" s="23"/>
-      <c r="U47" s="23"/>
+      <c r="S47" s="21"/>
+      <c r="U47" s="21"/>
       <c r="AI47" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ47" s="15" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AK47" s="15" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E48" s="8" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H48" s="10"/>
       <c r="I48" s="17"/>
       <c r="K48" s="17"/>
       <c r="M48" s="17"/>
       <c r="O48" s="17"/>
-      <c r="S48" s="23"/>
-      <c r="U48" s="23"/>
+      <c r="S48" s="21"/>
+      <c r="U48" s="21"/>
       <c r="AI48" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ48" s="15" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AK48" s="15" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E49" s="8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="H49" s="10"/>
       <c r="I49" s="17"/>
       <c r="K49" s="17"/>
       <c r="M49" s="17"/>
       <c r="O49" s="17"/>
-      <c r="S49" s="23"/>
-      <c r="U49" s="23"/>
+      <c r="S49" s="21"/>
+      <c r="U49" s="21"/>
       <c r="AI49" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ49" s="15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AK49" s="15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E50" s="8" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H50" s="10"/>
       <c r="I50" s="17"/>
       <c r="K50" s="17"/>
       <c r="M50" s="17"/>
       <c r="O50" s="17"/>
-      <c r="S50" s="23"/>
-      <c r="U50" s="23"/>
+      <c r="S50" s="21"/>
+      <c r="U50" s="21"/>
       <c r="AI50" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ50" s="15" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AK50" s="15" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E51" s="8" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H51" s="10"/>
       <c r="I51" s="17"/>
       <c r="K51" s="17"/>
       <c r="M51" s="17"/>
       <c r="O51" s="17"/>
-      <c r="S51" s="23"/>
-      <c r="U51" s="23"/>
+      <c r="S51" s="21"/>
+      <c r="U51" s="21"/>
       <c r="AI51" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ51" s="15" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AK51" s="15" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E52" s="8" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H52" s="10"/>
       <c r="I52" s="17"/>
       <c r="K52" s="17"/>
       <c r="M52" s="17"/>
       <c r="O52" s="17"/>
-      <c r="S52" s="23"/>
-      <c r="U52" s="23"/>
+      <c r="S52" s="21"/>
+      <c r="U52" s="21"/>
       <c r="AI52" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ52" s="15" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AK52" s="15" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E53" s="8" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H53" s="10"/>
       <c r="I53" s="17"/>
       <c r="K53" s="17"/>
       <c r="M53" s="17"/>
       <c r="O53" s="17"/>
-      <c r="S53" s="23"/>
-      <c r="U53" s="23"/>
+      <c r="S53" s="21"/>
+      <c r="U53" s="21"/>
       <c r="AI53" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ53" s="15" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AK53" s="15" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E54" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H54" s="10"/>
       <c r="I54" s="17"/>
       <c r="K54" s="17"/>
       <c r="M54" s="17"/>
       <c r="O54" s="17"/>
-      <c r="S54" s="23"/>
-      <c r="U54" s="23"/>
+      <c r="S54" s="21"/>
+      <c r="U54" s="21"/>
       <c r="AI54" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ54" s="15" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AK54" s="15" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E55" s="8" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H55" s="10"/>
       <c r="I55" s="17"/>
       <c r="K55" s="17"/>
       <c r="M55" s="17"/>
       <c r="O55" s="17"/>
-      <c r="S55" s="23"/>
-      <c r="U55" s="23"/>
+      <c r="S55" s="21"/>
+      <c r="U55" s="21"/>
       <c r="AI55" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ55" s="15" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AK55" s="15" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E56" s="8" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H56" s="10"/>
       <c r="I56" s="17"/>
       <c r="K56" s="17"/>
       <c r="M56" s="17"/>
       <c r="O56" s="17"/>
-      <c r="S56" s="23"/>
-      <c r="U56" s="23"/>
+      <c r="S56" s="21"/>
+      <c r="U56" s="21"/>
       <c r="AI56" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ56" s="15" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AK56" s="15" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E57" s="16" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="H57" s="10"/>
       <c r="I57" s="17"/>
       <c r="K57" s="17"/>
       <c r="M57" s="17"/>
       <c r="O57" s="17"/>
-      <c r="S57" s="23"/>
-      <c r="U57" s="23"/>
+      <c r="S57" s="21"/>
+      <c r="U57" s="21"/>
       <c r="AI57" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ57" s="15" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AK57" s="15" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G58" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="H58" s="10"/>
       <c r="I58" s="17"/>
       <c r="K58" s="17"/>
       <c r="M58" s="17"/>
       <c r="O58" s="17"/>
-      <c r="S58" s="23"/>
-      <c r="U58" s="23"/>
+      <c r="S58" s="21"/>
+      <c r="U58" s="21"/>
       <c r="AI58" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ58" s="15" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AK58" s="15" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G59" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H59" s="10"/>
       <c r="I59" s="17"/>
       <c r="K59" s="17"/>
       <c r="M59" s="17"/>
       <c r="O59" s="17"/>
-      <c r="S59" s="23"/>
-      <c r="U59" s="23"/>
+      <c r="S59" s="21"/>
+      <c r="U59" s="21"/>
       <c r="AI59" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ59" s="15" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AK59" s="15" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G60" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H60" s="10"/>
       <c r="I60" s="17"/>
       <c r="K60" s="17"/>
       <c r="M60" s="17"/>
       <c r="O60" s="17"/>
-      <c r="S60" s="23"/>
-      <c r="U60" s="23"/>
+      <c r="S60" s="21"/>
+      <c r="U60" s="21"/>
       <c r="AI60" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ60" s="15" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AK60" s="15" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G61" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="H61" s="10"/>
       <c r="I61" s="17"/>
       <c r="K61" s="17"/>
       <c r="M61" s="17"/>
       <c r="O61" s="17"/>
-      <c r="S61" s="23"/>
-      <c r="U61" s="23"/>
+      <c r="S61" s="21"/>
+      <c r="U61" s="21"/>
       <c r="AI61" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ61" s="15" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AK61" s="15" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G62" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H62" s="10"/>
       <c r="I62" s="17"/>
       <c r="K62" s="17"/>
       <c r="M62" s="17"/>
       <c r="O62" s="17"/>
-      <c r="S62" s="23"/>
-      <c r="U62" s="23"/>
+      <c r="S62" s="21"/>
+      <c r="U62" s="21"/>
       <c r="AI62" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ62" s="15" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AK62" s="15" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G63" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="H63" s="10"/>
       <c r="I63" s="17"/>
       <c r="K63" s="17"/>
       <c r="M63" s="17"/>
       <c r="O63" s="17"/>
-      <c r="S63" s="23"/>
-      <c r="U63" s="23"/>
+      <c r="S63" s="21"/>
+      <c r="U63" s="21"/>
       <c r="AI63" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ63" s="15" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AK63" s="15" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G64" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H64" s="10"/>
       <c r="I64" s="17"/>
       <c r="K64" s="17"/>
       <c r="M64" s="17"/>
       <c r="O64" s="17"/>
-      <c r="S64" s="23"/>
-      <c r="U64" s="23"/>
+      <c r="S64" s="21"/>
+      <c r="U64" s="21"/>
       <c r="AI64" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ64" s="15" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AK64" s="15" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G65" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H65" s="10"/>
       <c r="I65" s="17"/>
       <c r="K65" s="17"/>
       <c r="M65" s="17"/>
       <c r="O65" s="17"/>
-      <c r="S65" s="23"/>
-      <c r="U65" s="23"/>
+      <c r="S65" s="21"/>
+      <c r="U65" s="21"/>
       <c r="AI65" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ65" s="15" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AK65" s="15" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G66" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H66" s="10"/>
       <c r="I66" s="17"/>
       <c r="K66" s="17"/>
       <c r="M66" s="17"/>
       <c r="O66" s="17"/>
-      <c r="S66" s="23"/>
-      <c r="U66" s="23"/>
+      <c r="S66" s="21"/>
+      <c r="U66" s="21"/>
       <c r="AI66" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ66" s="15" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AK66" s="15" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G67" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H67" s="10"/>
       <c r="I67" s="17"/>
       <c r="K67" s="17"/>
       <c r="M67" s="17"/>
       <c r="O67" s="17"/>
-      <c r="S67" s="23"/>
-      <c r="U67" s="23"/>
+      <c r="S67" s="21"/>
+      <c r="U67" s="21"/>
       <c r="AI67" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ67" s="15" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AK67" s="15" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G68" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H68" s="10"/>
       <c r="I68" s="17"/>
       <c r="K68" s="17"/>
       <c r="M68" s="17"/>
       <c r="O68" s="17"/>
-      <c r="S68" s="23"/>
-      <c r="U68" s="23"/>
+      <c r="S68" s="21"/>
+      <c r="U68" s="21"/>
       <c r="AI68" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ68" s="15" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AK68" s="15" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G69" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H69" s="10"/>
       <c r="I69" s="17"/>
       <c r="K69" s="17"/>
       <c r="M69" s="17"/>
       <c r="O69" s="17"/>
-      <c r="S69" s="23"/>
-      <c r="U69" s="23"/>
+      <c r="S69" s="21"/>
+      <c r="U69" s="21"/>
       <c r="AI69" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ69" s="15" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AK69" s="15" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G70" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="H70" s="10"/>
       <c r="I70" s="17"/>
       <c r="K70" s="17"/>
       <c r="M70" s="17"/>
       <c r="O70" s="17"/>
-      <c r="S70" s="23"/>
-      <c r="U70" s="23"/>
+      <c r="S70" s="21"/>
+      <c r="U70" s="21"/>
       <c r="AI70" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ70" s="15" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AK70" s="15" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G71" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H71" s="10"/>
       <c r="I71" s="17"/>
       <c r="K71" s="17"/>
       <c r="M71" s="17"/>
       <c r="O71" s="17"/>
-      <c r="S71" s="23"/>
-      <c r="U71" s="23"/>
+      <c r="S71" s="21"/>
+      <c r="U71" s="21"/>
       <c r="AI71" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ71" s="15" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AK71" s="15" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G72" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H72" s="10"/>
       <c r="I72" s="17"/>
       <c r="K72" s="17"/>
       <c r="M72" s="17"/>
       <c r="O72" s="17"/>
-      <c r="S72" s="23"/>
-      <c r="U72" s="23"/>
+      <c r="S72" s="21"/>
+      <c r="U72" s="21"/>
       <c r="AI72" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ72" s="15" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AK72" s="15" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G73" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H73" s="10"/>
       <c r="I73" s="17"/>
       <c r="K73" s="17"/>
       <c r="M73" s="17"/>
       <c r="O73" s="17"/>
-      <c r="S73" s="23"/>
-      <c r="U73" s="23"/>
+      <c r="S73" s="21"/>
+      <c r="U73" s="21"/>
       <c r="AI73" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ73" s="15" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AK73" s="15" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G74" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="H74" s="10"/>
       <c r="I74" s="17"/>
       <c r="K74" s="17"/>
       <c r="M74" s="17"/>
       <c r="O74" s="17"/>
-      <c r="S74" s="23"/>
-      <c r="U74" s="23"/>
+      <c r="S74" s="21"/>
+      <c r="U74" s="21"/>
       <c r="AI74" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ74" s="15" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AK74" s="15" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G75" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H75" s="10"/>
       <c r="I75" s="17"/>
       <c r="K75" s="17"/>
       <c r="M75" s="17"/>
       <c r="O75" s="17"/>
-      <c r="S75" s="23"/>
-      <c r="U75" s="23"/>
+      <c r="S75" s="21"/>
+      <c r="U75" s="21"/>
       <c r="AI75" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ75" s="15" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AK75" s="15" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G76" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="H76" s="10"/>
       <c r="I76" s="17"/>
       <c r="K76" s="17"/>
       <c r="M76" s="17"/>
       <c r="O76" s="17"/>
-      <c r="S76" s="23"/>
-      <c r="U76" s="23"/>
+      <c r="S76" s="21"/>
+      <c r="U76" s="21"/>
       <c r="AI76" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ76" s="15" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AK76" s="15" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G77" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H77" s="10"/>
       <c r="I77" s="17"/>
       <c r="K77" s="17"/>
       <c r="M77" s="17"/>
       <c r="O77" s="17"/>
-      <c r="S77" s="23"/>
-      <c r="U77" s="23"/>
+      <c r="S77" s="21"/>
+      <c r="U77" s="21"/>
       <c r="AI77" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ77" s="15" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AK77" s="15" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G78" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="H78" s="10"/>
       <c r="I78" s="17"/>
       <c r="K78" s="17"/>
       <c r="M78" s="17"/>
       <c r="O78" s="17"/>
-      <c r="S78" s="23"/>
+      <c r="S78" s="21"/>
       <c r="AI78" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ78" s="15" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AK78" s="15" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G79" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="H79" s="10"/>
       <c r="I79" s="17"/>
       <c r="K79" s="17"/>
       <c r="M79" s="17"/>
       <c r="O79" s="17"/>
-      <c r="S79" s="23"/>
+      <c r="S79" s="21"/>
       <c r="AI79" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ79" s="15" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AK79" s="15" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G80" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="H80" s="10"/>
       <c r="I80" s="17"/>
       <c r="K80" s="17"/>
       <c r="M80" s="17"/>
       <c r="O80" s="17"/>
-      <c r="S80" s="23"/>
+      <c r="S80" s="21"/>
       <c r="AI80" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ80" s="15" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AK80" s="15" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G81" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="H81" s="10"/>
       <c r="I81" s="17"/>
       <c r="K81" s="17"/>
       <c r="M81" s="17"/>
       <c r="O81" s="17"/>
-      <c r="S81" s="23"/>
+      <c r="S81" s="21"/>
       <c r="AI81" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ81" s="15" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AK81" s="15" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G82" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="H82" s="10"/>
       <c r="I82" s="17"/>
       <c r="K82" s="17"/>
       <c r="M82" s="17"/>
       <c r="O82" s="17"/>
-      <c r="S82" s="23"/>
+      <c r="S82" s="21"/>
       <c r="AI82" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ82" s="15" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AK82" s="15" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G83" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H83" s="10"/>
       <c r="I83" s="17"/>
       <c r="K83" s="17"/>
       <c r="M83" s="17"/>
       <c r="O83" s="17"/>
-      <c r="S83" s="23"/>
+      <c r="S83" s="21"/>
       <c r="AI83" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ83" s="15" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AK83" s="15" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G84" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="H84" s="10"/>
       <c r="I84" s="17"/>
       <c r="K84" s="17"/>
       <c r="M84" s="17"/>
       <c r="O84" s="17"/>
-      <c r="S84" s="23"/>
+      <c r="S84" s="21"/>
       <c r="AI84" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ84" s="15" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AK84" s="15" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G85" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="H85" s="10"/>
       <c r="I85" s="17"/>
       <c r="K85" s="17"/>
       <c r="M85" s="17"/>
       <c r="O85" s="17"/>
-      <c r="S85" s="23"/>
+      <c r="S85" s="21"/>
       <c r="AI85" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ85" s="15" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AK85" s="15" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G86" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="H86" s="10"/>
       <c r="I86" s="17"/>
       <c r="K86" s="17"/>
       <c r="M86" s="17"/>
       <c r="O86" s="17"/>
-      <c r="S86" s="23"/>
+      <c r="S86" s="21"/>
       <c r="AI86" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ86" s="15" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AK86" s="15" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G87" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H87" s="10"/>
       <c r="I87" s="17"/>
       <c r="K87" s="17"/>
       <c r="M87" s="17"/>
       <c r="O87" s="17"/>
-      <c r="S87" s="23"/>
+      <c r="S87" s="21"/>
       <c r="AI87" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ87" s="15" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AK87" s="15" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G88" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H88" s="10"/>
       <c r="I88" s="17"/>
       <c r="K88" s="17"/>
       <c r="M88" s="17"/>
       <c r="O88" s="17"/>
-      <c r="S88" s="23"/>
+      <c r="S88" s="21"/>
       <c r="AI88" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ88" s="15" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AK88" s="15" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G89" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="H89" s="10"/>
       <c r="I89" s="17"/>
       <c r="K89" s="17"/>
       <c r="M89" s="17"/>
       <c r="O89" s="17"/>
-      <c r="S89" s="23"/>
-      <c r="V89" s="24"/>
-      <c r="W89" s="23"/>
+      <c r="S89" s="21"/>
+      <c r="V89" s="22"/>
+      <c r="W89" s="21"/>
       <c r="AI89" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ89" s="15" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AK89" s="15" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G90" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="H90" s="10"/>
       <c r="I90" s="17"/>
       <c r="K90" s="17"/>
       <c r="M90" s="17"/>
       <c r="O90" s="17"/>
-      <c r="S90" s="23"/>
-      <c r="V90" s="24"/>
-      <c r="W90" s="23"/>
+      <c r="S90" s="21"/>
+      <c r="V90" s="22"/>
+      <c r="W90" s="21"/>
       <c r="AI90" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ90" s="15" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AK90" s="15" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G91" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="H91" s="10"/>
       <c r="I91" s="17"/>
       <c r="K91" s="17"/>
       <c r="M91" s="17"/>
       <c r="O91" s="17"/>
-      <c r="S91" s="23"/>
-      <c r="V91" s="24"/>
-      <c r="W91" s="23"/>
+      <c r="S91" s="21"/>
+      <c r="V91" s="22"/>
+      <c r="W91" s="21"/>
       <c r="AI91" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ91" s="15" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AK91" s="15" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G92" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="H92" s="10"/>
       <c r="I92" s="17"/>
       <c r="K92" s="17"/>
       <c r="M92" s="17"/>
       <c r="O92" s="17"/>
-      <c r="S92" s="23"/>
-      <c r="V92" s="24"/>
-      <c r="W92" s="23"/>
+      <c r="S92" s="21"/>
+      <c r="V92" s="22"/>
+      <c r="W92" s="21"/>
       <c r="AI92" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ92" s="15" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AK92" s="15" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G93" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="S93" s="23"/>
-      <c r="V93" s="24"/>
-      <c r="W93" s="23"/>
+        <v>384</v>
+      </c>
+      <c r="S93" s="21"/>
+      <c r="V93" s="22"/>
+      <c r="W93" s="21"/>
       <c r="AI93" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ93" s="15" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AK93" s="15" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G94" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="S94" s="23"/>
-      <c r="V94" s="24"/>
-      <c r="W94" s="23"/>
+        <v>387</v>
+      </c>
+      <c r="S94" s="21"/>
+      <c r="V94" s="22"/>
+      <c r="W94" s="21"/>
       <c r="AI94" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ94" s="15" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AK94" s="15" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G95" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="S95" s="23"/>
-      <c r="V95" s="24"/>
-      <c r="W95" s="23"/>
+        <v>389</v>
+      </c>
+      <c r="S95" s="21"/>
+      <c r="V95" s="22"/>
+      <c r="W95" s="21"/>
       <c r="AI95" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ95" s="15" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AK95" s="15" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G96" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="S96" s="23"/>
-      <c r="V96" s="24"/>
-      <c r="W96" s="23"/>
+        <v>392</v>
+      </c>
+      <c r="S96" s="21"/>
+      <c r="V96" s="22"/>
+      <c r="W96" s="21"/>
       <c r="AI96" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ96" s="15" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AK96" s="15" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G97" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AI97" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ97" s="15" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AK97" s="15" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G98" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AI98" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ98" s="15" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AK98" s="15" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G99" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AI99" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ99" s="15" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AK99" s="15" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G100" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AI100" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ100" s="15" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AK100" s="15" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G101" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AI101" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ101" s="15" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AK101" s="15" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G102" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AI102" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ102" s="15" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AK102" s="15" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G103" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AI103" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ103" s="15" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AK103" s="15" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G104" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AI104" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ104" s="15" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AK104" s="15" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G105" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AI105" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ105" s="15" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AK105" s="15" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G106" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AI106" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ106" s="15" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AK106" s="15" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G107" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AI107" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ107" s="15" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AK107" s="15" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G108" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AI108" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ108" s="15" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AK108" s="15" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G109" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="AI109" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ109" s="15" t="s">
         <v>418</v>
       </c>
-      <c r="AI109" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ109" s="15" t="s">
-        <v>416</v>
-      </c>
       <c r="AK109" s="15" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G110" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AI110" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ110" s="15" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AK110" s="15" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G111" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AI111" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ111" s="15" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AK111" s="15" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G112" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AI112" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ112" s="15" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AK112" s="15" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G113" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AI113" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ113" s="15" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AK113" s="15" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G114" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="AI114" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ114" s="15" t="s">
         <v>430</v>
       </c>
-      <c r="AI114" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ114" s="15" t="s">
-        <v>428</v>
-      </c>
       <c r="AK114" s="15" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G115" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AI115" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ115" s="15" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AK115" s="15" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G116" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AI116" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ116" s="15" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AK116" s="15" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G117" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AI117" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ117" s="15" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AK117" s="15" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G118" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="AI118" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ118" s="15" t="s">
         <v>441</v>
       </c>
-      <c r="AI118" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ118" s="15" t="s">
-        <v>439</v>
-      </c>
       <c r="AK118" s="15" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G119" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AI119" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ119" s="15" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AK119" s="15" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G120" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AI120" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ120" s="15" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AK120" s="15" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G121" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AI121" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ121" s="15" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AK121" s="15" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G122" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AI122" s="15" t="s">
         <v>51</v>
       </c>
       <c r="AJ122" s="15" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AK122" s="15" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G123" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="AI123" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ123" s="15" t="s">
         <v>454</v>
       </c>
-      <c r="AI123" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ123" s="15" t="s">
-        <v>452</v>
-      </c>
       <c r="AK123" s="15" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G124" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AI124" s="15" t="s">
-        <v>457</v>
+        <v>51</v>
       </c>
       <c r="AJ124" s="15" t="s">
-        <v>36</v>
+        <v>459</v>
       </c>
       <c r="AK124" s="15" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G125" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AI125" s="15" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="AJ125" s="15" t="s">
         <v>36</v>
       </c>
       <c r="AK125" s="15" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G126" s="1" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AI126" s="15" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="AJ126" s="15" t="s">
         <v>36</v>
       </c>
       <c r="AK126" s="15" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G127" s="1" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AI127" s="15" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="AJ127" s="15" t="s">
         <v>36</v>
       </c>
       <c r="AK127" s="15" t="s">
-        <v>350</v>
+        <v>467</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G128" s="1" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="AI128" s="15" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="AJ128" s="15" t="s">
         <v>36</v>
       </c>
       <c r="AK128" s="15" t="s">
-        <v>36</v>
+        <v>352</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G129" s="1" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AI129" s="15" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="AJ129" s="15" t="s">
         <v>36</v>
       </c>
       <c r="AK129" s="15" t="s">
-        <v>350</v>
+        <v>36</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G130" s="1" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="AI130" s="15" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AJ130" s="15" t="s">
         <v>36</v>
       </c>
       <c r="AK130" s="15" t="s">
-        <v>36</v>
+        <v>352</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G131" s="1" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AI131" s="15" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AJ131" s="15" t="s">
-        <v>36</v>
+        <v>473</v>
       </c>
       <c r="AK131" s="15" t="s">
-        <v>350</v>
+        <v>474</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G132" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="AI132" s="15" t="s">
         <v>470</v>
       </c>
-      <c r="AI132" s="15" t="s">
-        <v>471</v>
-      </c>
       <c r="AJ132" s="15" t="s">
-        <v>36</v>
+        <v>476</v>
       </c>
       <c r="AK132" s="15" t="s">
-        <v>36</v>
+        <v>476</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G133" s="1" t="s">
+        <v>477</v>
+      </c>
       <c r="AI133" s="15" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="AJ133" s="15" t="s">
         <v>36</v>
@@ -5066,18 +5164,18 @@
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI134" s="15" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="AJ134" s="15" t="s">
         <v>36</v>
       </c>
       <c r="AK134" s="15" t="s">
-        <v>36</v>
+        <v>352</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI135" s="15" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="AJ135" s="15" t="s">
         <v>36</v>
@@ -5088,7 +5186,7 @@
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI136" s="15" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="AJ136" s="15" t="s">
         <v>36</v>
@@ -5099,7 +5197,7 @@
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI137" s="15" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="AJ137" s="15" t="s">
         <v>36</v>
@@ -5110,7 +5208,7 @@
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI138" s="15" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="AJ138" s="15" t="s">
         <v>36</v>
@@ -5121,7 +5219,7 @@
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI139" s="15" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="AJ139" s="15" t="s">
         <v>36</v>
@@ -5132,7 +5230,7 @@
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI140" s="15" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="AJ140" s="15" t="s">
         <v>36</v>
@@ -5142,15 +5240,53 @@
       </c>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AI141" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="AJ141" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="AK141" s="1" t="s">
+      <c r="AI141" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="AJ141" s="15" t="s">
         <v>36</v>
       </c>
+      <c r="AK141" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI142" s="15" t="s">
+        <v>486</v>
+      </c>
+      <c r="AJ142" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK142" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI143" s="15" t="s">
+        <v>487</v>
+      </c>
+      <c r="AJ143" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK143" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI144" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="AJ144" s="15" t="s">
+        <v>489</v>
+      </c>
+      <c r="AK144" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI145" s="15"/>
+      <c r="AJ145" s="15"/>
+      <c r="AK145" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5171,23 +5307,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D131"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="52.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="2.54"/>
-  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C1" s="1" t="n">
-        <v>0</v>
+        <v>490</v>
       </c>
       <c r="D1" s="1" t="n">
         <v>1</v>
@@ -5198,10 +5326,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>1</v>
+        <v>491</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>1</v>
@@ -5212,10 +5337,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>1</v>
+        <v>492</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>1</v>
@@ -5226,10 +5348,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>0</v>
+        <v>493</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>1</v>
@@ -5240,10 +5359,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>0</v>
+        <v>494</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>1</v>
@@ -5254,10 +5370,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>0</v>
+        <v>495</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>1</v>
@@ -5268,10 +5381,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>0</v>
+        <v>496</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>1</v>
@@ -5282,10 +5392,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>0</v>
+        <v>490</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>1</v>
@@ -5296,10 +5403,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>1</v>
@@ -5310,10 +5414,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C10" s="1" t="n">
-        <v>1</v>
+        <v>498</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>1</v>
@@ -5324,10 +5425,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>1</v>
+        <v>499</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>1</v>
@@ -5338,10 +5436,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>1</v>
@@ -5352,10 +5447,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C13" s="1" t="n">
-        <v>0</v>
+        <v>501</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>1</v>
@@ -5366,10 +5458,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C14" s="1" t="n">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>1</v>
@@ -5380,10 +5469,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C15" s="1" t="n">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>1</v>
@@ -5394,10 +5480,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C16" s="1" t="n">
-        <v>0</v>
+        <v>503</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>1</v>
@@ -5408,10 +5491,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="C17" s="1" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>1</v>
@@ -5422,10 +5502,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C18" s="1" t="n">
-        <v>0</v>
+        <v>505</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>1</v>
@@ -5436,10 +5513,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C19" s="1" t="n">
-        <v>0</v>
+        <v>506</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>1</v>
@@ -5450,10 +5524,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C20" s="1" t="n">
-        <v>0</v>
+        <v>507</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>1</v>
@@ -5464,10 +5535,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C21" s="1" t="n">
-        <v>0</v>
+        <v>508</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>1</v>
@@ -5478,10 +5546,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C22" s="1" t="n">
-        <v>0</v>
+        <v>509</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>1</v>
@@ -5492,10 +5557,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C23" s="1" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>1</v>
@@ -5506,1510 +5568,9 @@
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C24" s="1" t="n">
-        <v>0</v>
+        <v>511</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="C25" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="C26" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="C27" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="C28" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C29" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="C30" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="C31" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C32" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="C33" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C34" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="n">
-        <v>43</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="C38" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="n">
-        <v>45</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="C39" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="n">
-        <v>46</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="C40" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="n">
-        <v>47</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C41" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="n">
-        <v>48</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C42" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="n">
-        <v>49</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C43" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="C44" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="n">
-        <v>51</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="C45" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="n">
-        <v>52</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="C46" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="n">
-        <v>53</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="C47" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="n">
-        <v>54</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="C48" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="n">
-        <v>55</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C49" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="n">
-        <v>56</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="C50" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="n">
-        <v>57</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="C51" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="n">
-        <v>58</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C52" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="n">
-        <v>59</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="C53" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D53" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="C54" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="n">
-        <v>61</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="C55" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="n">
-        <v>62</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="C56" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D56" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="n">
-        <v>63</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="C57" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="n">
-        <v>64</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="C58" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="n">
-        <v>65</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="C59" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="n">
-        <v>66</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="C60" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="n">
-        <v>67</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="C61" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="n">
-        <v>68</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="C62" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="n">
-        <v>69</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="C63" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="n">
-        <v>70</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="C64" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="n">
-        <v>71</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="C65" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1" t="n">
-        <v>72</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="C66" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D66" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="n">
-        <v>73</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="C67" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D67" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="n">
-        <v>74</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="C68" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D68" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="n">
-        <v>75</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="C69" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D69" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="n">
-        <v>76</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C70" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D70" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="n">
-        <v>77</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="C71" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D71" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="n">
-        <v>78</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="C72" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D72" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="n">
-        <v>79</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="C73" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="n">
-        <v>80</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="C74" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="n">
-        <v>81</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="C75" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D75" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="n">
-        <v>82</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="C76" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D76" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="n">
-        <v>83</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="C77" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="n">
-        <v>84</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="C78" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D78" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="n">
-        <v>85</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="C79" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D79" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="n">
-        <v>86</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="C80" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="n">
-        <v>87</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="C81" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D81" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="n">
-        <v>88</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="C82" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D82" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="n">
-        <v>89</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="C83" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="n">
-        <v>90</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="C84" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="n">
-        <v>91</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="C85" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D85" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="n">
-        <v>92</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="C86" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D86" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="n">
-        <v>93</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="C87" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="C88" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D88" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="C89" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D89" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="1" t="n">
-        <v>96</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="C90" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D90" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1" t="n">
-        <v>97</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="C91" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="1" t="n">
-        <v>98</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="C92" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D92" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1" t="n">
-        <v>99</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="C93" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D93" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="C94" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D94" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="1" t="n">
-        <v>101</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="C95" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="1" t="n">
-        <v>102</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="C96" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="1" t="n">
-        <v>103</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="C97" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D97" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="1" t="n">
-        <v>104</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="C98" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D98" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="1" t="n">
-        <v>105</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="C99" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D99" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="1" t="n">
-        <v>106</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="C100" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D100" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="1" t="n">
-        <v>107</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="C101" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="1" t="n">
-        <v>108</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C102" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="1" t="n">
-        <v>109</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="C103" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D103" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="1" t="n">
-        <v>110</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="C104" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D104" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="1" t="n">
-        <v>111</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="C105" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D105" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="1" t="n">
-        <v>112</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="C106" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D106" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="1" t="n">
-        <v>113</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="C107" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D107" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="1" t="n">
-        <v>114</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="C108" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D108" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="1" t="n">
-        <v>115</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="C109" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D109" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="1" t="n">
-        <v>116</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="C110" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D110" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="1" t="n">
-        <v>117</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="C111" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D111" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="1" t="n">
-        <v>118</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="C112" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D112" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="1" t="n">
-        <v>119</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="C113" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D113" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="1" t="n">
-        <v>120</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="C114" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D114" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="1" t="n">
-        <v>121</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="C115" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D115" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="1" t="n">
-        <v>122</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="C116" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D116" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="1" t="n">
-        <v>123</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="C117" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D117" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="1" t="n">
-        <v>124</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="C118" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D118" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="1" t="n">
-        <v>125</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="C119" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D119" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="1" t="n">
-        <v>126</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="C120" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D120" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="1" t="n">
-        <v>127</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="C121" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D121" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="1" t="n">
-        <v>128</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="C122" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D122" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="1" t="n">
-        <v>129</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="C123" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D123" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="1" t="n">
-        <v>130</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="C124" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D124" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="1" t="n">
-        <v>131</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="C125" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D125" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="1" t="n">
-        <v>132</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="C126" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D126" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="1" t="n">
-        <v>133</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="C127" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D127" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="1" t="n">
-        <v>134</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="C128" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D128" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="1" t="n">
-        <v>135</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="C129" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D129" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="1" t="n">
-        <v>136</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="C130" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D130" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="1" t="n">
-        <v>137</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="C131" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D131" s="1" t="n">
         <v>1</v>
       </c>
     </row>

--- a/storage/app/public/glosario.xlsx
+++ b/storage/app/public/glosario.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="523">
   <si>
     <t xml:space="preserve">utiliza_transporte</t>
   </si>
@@ -809,7 +809,7 @@
     <t xml:space="preserve">Analista De Planificación Y Control De Gestion</t>
   </si>
   <si>
-    <t xml:space="preserve">Redes Sociales (RRSS)</t>
+    <t xml:space="preserve">Redes Sociales (rrss)</t>
   </si>
   <si>
     <t xml:space="preserve">la rinconada</t>
@@ -1409,52 +1409,85 @@
     <t xml:space="preserve">Asistente de Marca</t>
   </si>
   <si>
+    <t xml:space="preserve">Kia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kia Encuestas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ejecutivo Comercial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Librepago G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backoffice de Mercadeo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Di Stasi Motors G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asesor Comercial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corpocredit G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supervisor de Ventas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G-talent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordinadora de Captación y Selección de  Talentos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ubii Pagos Cobranzas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordinador de Mercadeo y RRPP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oceanica De Seguros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ventas Oceanica De Seguros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analista de Back Office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cobranzas Oceanica De Seguros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supervisor Senior de BackOffice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jac Motors</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gerencia de Formacion y Calidad</t>
   </si>
   <si>
     <t xml:space="preserve">Formación</t>
   </si>
   <si>
-    <t xml:space="preserve">Ejecutivo Comercial</t>
-  </si>
-  <si>
     <t xml:space="preserve">Calidad</t>
   </si>
   <si>
-    <t xml:space="preserve">Backoffice de Mercadeo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Captación</t>
   </si>
   <si>
-    <t xml:space="preserve">Asesor Comercial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supervisor de Ventas</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gerencia Business Intelligence</t>
   </si>
   <si>
-    <t xml:space="preserve">Coordinadora de Captación y Selección de  Talentos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coordinador de Mercadeo y RRPP</t>
-  </si>
-  <si>
     <t xml:space="preserve">Backoffice</t>
   </si>
   <si>
     <t xml:space="preserve">Backoficce</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista de Back Office</t>
-  </si>
-  <si>
     <t xml:space="preserve">Formacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supervisor Senior de BackOffice</t>
   </si>
   <si>
     <t xml:space="preserve">Gerencia De Tecnología</t>
@@ -1979,7 +2012,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AM145"/>
+  <dimension ref="A1:AM154"/>
   <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.67"/>
@@ -5041,10 +5074,10 @@
         <v>461</v>
       </c>
       <c r="AI125" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ125" s="15" t="s">
         <v>462</v>
-      </c>
-      <c r="AJ125" s="15" t="s">
-        <v>36</v>
       </c>
       <c r="AK125" s="15" t="s">
         <v>463</v>
@@ -5055,10 +5088,10 @@
         <v>464</v>
       </c>
       <c r="AI126" s="15" t="s">
-        <v>462</v>
+        <v>51</v>
       </c>
       <c r="AJ126" s="15" t="s">
-        <v>36</v>
+        <v>465</v>
       </c>
       <c r="AK126" s="15" t="s">
         <v>465</v>
@@ -5069,10 +5102,10 @@
         <v>466</v>
       </c>
       <c r="AI127" s="15" t="s">
-        <v>462</v>
+        <v>51</v>
       </c>
       <c r="AJ127" s="15" t="s">
-        <v>36</v>
+        <v>467</v>
       </c>
       <c r="AK127" s="15" t="s">
         <v>467</v>
@@ -5083,116 +5116,116 @@
         <v>468</v>
       </c>
       <c r="AI128" s="15" t="s">
-        <v>462</v>
+        <v>51</v>
       </c>
       <c r="AJ128" s="15" t="s">
-        <v>36</v>
+        <v>469</v>
       </c>
       <c r="AK128" s="15" t="s">
-        <v>352</v>
+        <v>469</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G129" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AI129" s="15" t="s">
-        <v>470</v>
+        <v>51</v>
       </c>
       <c r="AJ129" s="15" t="s">
-        <v>36</v>
+        <v>471</v>
       </c>
       <c r="AK129" s="15" t="s">
-        <v>36</v>
+        <v>471</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G130" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AI130" s="15" t="s">
-        <v>470</v>
+        <v>51</v>
       </c>
       <c r="AJ130" s="15" t="s">
-        <v>36</v>
+        <v>473</v>
       </c>
       <c r="AK130" s="15" t="s">
-        <v>352</v>
+        <v>473</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G131" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AI131" s="15" t="s">
-        <v>470</v>
+        <v>51</v>
       </c>
       <c r="AJ131" s="15" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AK131" s="15" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G132" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="AI132" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ132" s="15" t="s">
         <v>475</v>
       </c>
-      <c r="AI132" s="15" t="s">
-        <v>470</v>
-      </c>
-      <c r="AJ132" s="15" t="s">
-        <v>476</v>
-      </c>
       <c r="AK132" s="15" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G133" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AI133" s="15" t="s">
-        <v>478</v>
+        <v>51</v>
       </c>
       <c r="AJ133" s="15" t="s">
-        <v>36</v>
+        <v>480</v>
       </c>
       <c r="AK133" s="15" t="s">
-        <v>36</v>
+        <v>480</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI134" s="15" t="s">
-        <v>478</v>
+        <v>51</v>
       </c>
       <c r="AJ134" s="15" t="s">
-        <v>36</v>
+        <v>480</v>
       </c>
       <c r="AK134" s="15" t="s">
-        <v>352</v>
+        <v>480</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI135" s="15" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AJ135" s="15" t="s">
         <v>36</v>
       </c>
       <c r="AK135" s="15" t="s">
-        <v>36</v>
+        <v>482</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI136" s="15" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AJ136" s="15" t="s">
         <v>36</v>
       </c>
       <c r="AK136" s="15" t="s">
-        <v>36</v>
+        <v>483</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5203,23 +5236,23 @@
         <v>36</v>
       </c>
       <c r="AK137" s="15" t="s">
-        <v>36</v>
+        <v>484</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI138" s="15" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AJ138" s="15" t="s">
         <v>36</v>
       </c>
       <c r="AK138" s="15" t="s">
-        <v>36</v>
+        <v>352</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI139" s="15" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AJ139" s="15" t="s">
         <v>36</v>
@@ -5230,13 +5263,13 @@
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI140" s="15" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AJ140" s="15" t="s">
         <v>36</v>
       </c>
       <c r="AK140" s="15" t="s">
-        <v>36</v>
+        <v>352</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5244,26 +5277,26 @@
         <v>485</v>
       </c>
       <c r="AJ141" s="15" t="s">
-        <v>36</v>
+        <v>486</v>
       </c>
       <c r="AK141" s="15" t="s">
-        <v>36</v>
+        <v>487</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI142" s="15" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AJ142" s="15" t="s">
-        <v>36</v>
+        <v>488</v>
       </c>
       <c r="AK142" s="15" t="s">
-        <v>36</v>
+        <v>488</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI143" s="15" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AJ143" s="15" t="s">
         <v>36</v>
@@ -5274,19 +5307,124 @@
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI144" s="15" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AJ144" s="15" t="s">
-        <v>489</v>
+        <v>36</v>
       </c>
       <c r="AK144" s="15" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI145" s="15" t="s">
+        <v>490</v>
+      </c>
+      <c r="AJ145" s="15" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AI145" s="15"/>
-      <c r="AJ145" s="15"/>
-      <c r="AK145" s="15"/>
+      <c r="AK145" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI146" s="15" t="s">
+        <v>491</v>
+      </c>
+      <c r="AJ146" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK146" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI147" s="15" t="s">
+        <v>492</v>
+      </c>
+      <c r="AJ147" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK147" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI148" s="15" t="s">
+        <v>493</v>
+      </c>
+      <c r="AJ148" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK148" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI149" s="15" t="s">
+        <v>494</v>
+      </c>
+      <c r="AJ149" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK149" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI150" s="15" t="s">
+        <v>495</v>
+      </c>
+      <c r="AJ150" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK150" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI151" s="15" t="s">
+        <v>496</v>
+      </c>
+      <c r="AJ151" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK151" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI152" s="15" t="s">
+        <v>497</v>
+      </c>
+      <c r="AJ152" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK152" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI153" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="AJ153" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK153" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI154" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="AJ154" s="15" t="s">
+        <v>500</v>
+      </c>
+      <c r="AK154" s="15" t="s">
+        <v>36</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5315,7 +5453,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="D1" s="1" t="n">
         <v>1</v>
@@ -5326,7 +5464,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>1</v>
@@ -5337,7 +5475,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>1</v>
@@ -5348,7 +5486,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>1</v>
@@ -5359,7 +5497,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>1</v>
@@ -5370,7 +5508,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>1</v>
@@ -5381,7 +5519,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>1</v>
@@ -5392,7 +5530,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>1</v>
@@ -5403,7 +5541,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>1</v>
@@ -5414,7 +5552,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>1</v>
@@ -5425,7 +5563,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>1</v>
@@ -5436,7 +5574,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>1</v>
@@ -5447,7 +5585,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>1</v>
@@ -5458,7 +5596,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>1</v>
@@ -5469,7 +5607,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>1</v>
@@ -5480,7 +5618,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>1</v>
@@ -5491,7 +5629,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>1</v>
@@ -5502,7 +5640,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>1</v>
@@ -5513,7 +5651,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>1</v>
@@ -5524,7 +5662,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>1</v>
@@ -5535,7 +5673,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>1</v>
@@ -5546,7 +5684,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>1</v>
@@ -5557,7 +5695,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>510</v>
+        <v>521</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>1</v>
@@ -5568,7 +5706,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>1</v>

--- a/storage/app/public/glosario.xlsx
+++ b/storage/app/public/glosario.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="446">
   <si>
     <t xml:space="preserve">utiliza_transporte</t>
   </si>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">plaza venezuela</t>
   </si>
   <si>
-    <t xml:space="preserve">Supervisor de Gestion Operativa</t>
+    <t xml:space="preserve">Supervisor Operativo</t>
   </si>
   <si>
     <t xml:space="preserve">Lunes y Viernes</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">colegio de ingenieros</t>
   </si>
   <si>
-    <t xml:space="preserve">Supervisor Operativo</t>
+    <t xml:space="preserve">Recepcionista</t>
   </si>
   <si>
     <t xml:space="preserve">Lunes y Sabados</t>
@@ -443,7 +443,7 @@
     <t xml:space="preserve">bellas artes</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista</t>
+    <t xml:space="preserve">Customer Success Manager</t>
   </si>
   <si>
     <t xml:space="preserve">Martes y Jueves</t>
@@ -461,7 +461,7 @@
     <t xml:space="preserve">parque carabobo</t>
   </si>
   <si>
-    <t xml:space="preserve">Ejecutivo De ATC</t>
+    <t xml:space="preserve">Lider Tecnico De Producto</t>
   </si>
   <si>
     <t xml:space="preserve">Martes y Viernes</t>
@@ -479,7 +479,7 @@
     <t xml:space="preserve">la hoyada</t>
   </si>
   <si>
-    <t xml:space="preserve">Recepcionista</t>
+    <t xml:space="preserve">Psicologo Organizacional</t>
   </si>
   <si>
     <t xml:space="preserve">8:30 AM a 5:30 PM</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">capitolio</t>
   </si>
   <si>
-    <t xml:space="preserve">Validador</t>
+    <t xml:space="preserve">Vice-Presidente</t>
   </si>
   <si>
     <t xml:space="preserve">Martes y Sabado</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">caño amarillo</t>
   </si>
   <si>
-    <t xml:space="preserve">Chofer</t>
+    <t xml:space="preserve">Analista  Senior De Ingenieria De Software</t>
   </si>
   <si>
     <t xml:space="preserve">Martes y Domingos</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">agua salud</t>
   </si>
   <si>
-    <t xml:space="preserve">Community Manager</t>
+    <t xml:space="preserve">Analista Administrativo</t>
   </si>
   <si>
     <t xml:space="preserve">Miercoles y Viernes</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">gato negro</t>
   </si>
   <si>
-    <t xml:space="preserve">Customer Success Manager</t>
+    <t xml:space="preserve">Analista De Calidad</t>
   </si>
   <si>
     <t xml:space="preserve">Miercoles y Sabados</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">plaza sucre</t>
   </si>
   <si>
-    <t xml:space="preserve">Customer Technical Support Manager</t>
+    <t xml:space="preserve">Analista De Calidad Hi4Ai</t>
   </si>
   <si>
     <t xml:space="preserve">Miercoles y Domingos</t>
@@ -572,7 +572,7 @@
     <t xml:space="preserve">perez bonalde</t>
   </si>
   <si>
-    <t xml:space="preserve">Diseñador Grafico</t>
+    <t xml:space="preserve">Analista De Captacion Y Seleccion De Talento</t>
   </si>
   <si>
     <t xml:space="preserve">Jueves y Sabados</t>
@@ -587,7 +587,7 @@
     <t xml:space="preserve">propatria</t>
   </si>
   <si>
-    <t xml:space="preserve">Inside Sales</t>
+    <t xml:space="preserve">Analista De Gestion Humana</t>
   </si>
   <si>
     <t xml:space="preserve">Jueves y Domingos</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">el silencio</t>
   </si>
   <si>
-    <t xml:space="preserve">Lider Tecnico De Producto</t>
+    <t xml:space="preserve">Analista De Planificación Y Control De Gestion</t>
   </si>
   <si>
     <t xml:space="preserve">Viernes y Domingos</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">capuchinos</t>
   </si>
   <si>
-    <t xml:space="preserve">Psicologo Organizacional</t>
+    <t xml:space="preserve">Analista De Reclutamiento Bilingüe</t>
   </si>
   <si>
     <t xml:space="preserve">Rotativo</t>
@@ -632,7 +632,7 @@
     <t xml:space="preserve">maternidad</t>
   </si>
   <si>
-    <t xml:space="preserve">Software Development Specialist</t>
+    <t xml:space="preserve">Analista De Soporte Tecnico</t>
   </si>
   <si>
     <t xml:space="preserve">Cobranzas Residencial</t>
@@ -644,7 +644,7 @@
     <t xml:space="preserve">artigas</t>
   </si>
   <si>
-    <t xml:space="preserve">Technical Support Analyst</t>
+    <t xml:space="preserve">Analista Hi4Ai</t>
   </si>
   <si>
     <t xml:space="preserve">Atc Aba Ultra</t>
@@ -656,7 +656,7 @@
     <t xml:space="preserve">la paz</t>
   </si>
   <si>
-    <t xml:space="preserve">Vice-Presidente</t>
+    <t xml:space="preserve">Ejecutivo Telefonico</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -671,7 +671,7 @@
     <t xml:space="preserve">la yaguara</t>
   </si>
   <si>
-    <t xml:space="preserve">Gestor De Contenido</t>
+    <t xml:space="preserve">Coordinador(a) De Contabilidad</t>
   </si>
   <si>
     <t xml:space="preserve">Aba Ultra Empresas</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">carapita</t>
   </si>
   <si>
-    <t xml:space="preserve">Agente Auditor</t>
+    <t xml:space="preserve">Auxiliar I SSGG</t>
   </si>
   <si>
     <t xml:space="preserve">0800 Publica - Inbound</t>
@@ -695,7 +695,7 @@
     <t xml:space="preserve">antimano</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista  Senior De Ingenieria De Software</t>
+    <t xml:space="preserve">Gerente De Asuntos Legales</t>
   </si>
   <si>
     <t xml:space="preserve">0800 Empresa - Diferido</t>
@@ -704,7 +704,7 @@
     <t xml:space="preserve">mamera</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista Administrativo</t>
+    <t xml:space="preserve">Gerente De Bussiness Intelligence</t>
   </si>
   <si>
     <t xml:space="preserve">0800 Publica - Diferido</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">caricuao</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista Bussiness Intelligence</t>
+    <t xml:space="preserve">Gerente De Gestion Humana</t>
   </si>
   <si>
     <t xml:space="preserve">Digital Partner</t>
@@ -725,7 +725,7 @@
     <t xml:space="preserve">zoologico</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista De Administracion</t>
+    <t xml:space="preserve">Gerente De Mercadeo y RRPP</t>
   </si>
   <si>
     <t xml:space="preserve">Digital Partner - Scotiabank</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">ruiz pineda</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista De Calidad</t>
+    <t xml:space="preserve">Gerente De Negocios</t>
   </si>
   <si>
     <t xml:space="preserve">Digital Partner - Caja Los Andes</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">las adjuntas</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista De Calidad Hi4Ai</t>
+    <t xml:space="preserve">Gerente De Administracion y Finanzas</t>
   </si>
   <si>
     <t xml:space="preserve">Ibr</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">ciudad universitaria</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista De Captacion Y Seleccion De Talento</t>
+    <t xml:space="preserve">Gerente De Planificacion Y Control de Gestion</t>
   </si>
   <si>
     <t xml:space="preserve">Bupa</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">los simbolos</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista De Desarrollo Organizacional</t>
+    <t xml:space="preserve">Back Office</t>
   </si>
   <si>
     <t xml:space="preserve">Movistar</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">la bandera</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista De Gestion Humana</t>
+    <t xml:space="preserve">Analista Senior De Bussiness Intelligence</t>
   </si>
   <si>
     <t xml:space="preserve">Mda</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">el valle</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista De Ingeniería De Software</t>
+    <t xml:space="preserve">Senior De Soporte Tecnico</t>
   </si>
   <si>
     <t xml:space="preserve">Portabilidad Concentra</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">los jardines</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista De Mercadeo Y Comunicaciones</t>
+    <t xml:space="preserve">Coordinador(a) de Administranción y Finanzas</t>
   </si>
   <si>
     <t xml:space="preserve">Portamx Bdd</t>
@@ -797,7 +797,7 @@
     <t xml:space="preserve">coche</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista De Operaciones</t>
+    <t xml:space="preserve">Senior de Desarrollo Organizacional y Bienestar Social</t>
   </si>
   <si>
     <t xml:space="preserve">Marketing</t>
@@ -806,7 +806,7 @@
     <t xml:space="preserve">mercado</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista De Planificación Y Control De Gestion</t>
+    <t xml:space="preserve">Programador</t>
   </si>
   <si>
     <t xml:space="preserve">Redes Sociales (rrss)</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">la rinconada</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista De Reclutamiento Bilingüe</t>
+    <t xml:space="preserve">Especialista de Gestión Humana</t>
   </si>
   <si>
     <t xml:space="preserve">Cuballama</t>
@@ -824,7 +824,7 @@
     <t xml:space="preserve">zona rental</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista De Soporte Tecnico</t>
+    <t xml:space="preserve">Senior de Captación y Selección de Talento</t>
   </si>
   <si>
     <t xml:space="preserve">Movilnet</t>
@@ -833,7 +833,7 @@
     <t xml:space="preserve">parque central</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista Hi4Ai</t>
+    <t xml:space="preserve">Lider de Programación</t>
   </si>
   <si>
     <t xml:space="preserve">Movilnet Tlv</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">nuevo circo</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista Senior De Desarrollo Organizacional</t>
+    <t xml:space="preserve">Coordinador de Business Intelligence</t>
   </si>
   <si>
     <t xml:space="preserve">M1</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">teatros</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista Senior De Gestion Humana</t>
+    <t xml:space="preserve">Coordinador de Planificación y Control de la Gestión</t>
   </si>
   <si>
     <t xml:space="preserve">Unilever</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">bello monte</t>
   </si>
   <si>
-    <t xml:space="preserve">Ejecutivo(a) De Ventas</t>
+    <t xml:space="preserve">Senior de Nomina</t>
   </si>
   <si>
     <t xml:space="preserve">Enpro</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">charallave norte</t>
   </si>
   <si>
-    <t xml:space="preserve">Ejecutivo Telefonico</t>
+    <t xml:space="preserve">Coordinadora de Captación y Selección de  Talentos</t>
   </si>
   <si>
     <t xml:space="preserve">Rohr</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">charallave sur</t>
   </si>
   <si>
-    <t xml:space="preserve">Ejecutivo Telefónico De Captación</t>
+    <t xml:space="preserve">Coordinador de Mercadeo y RRPP</t>
   </si>
   <si>
     <t xml:space="preserve">Calox</t>
@@ -887,583 +887,352 @@
     <t xml:space="preserve">cua</t>
   </si>
   <si>
-    <t xml:space="preserve">Especialista De Finanzas</t>
+    <t xml:space="preserve">Supervisor Senior de BackOffice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calox Contigo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ocumare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supervisor de SSGG</t>
   </si>
   <si>
     <t xml:space="preserve">Portabilidad Peru</t>
   </si>
   <si>
-    <t xml:space="preserve">ocumare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Especialista De PyCG</t>
+    <t xml:space="preserve">guarenas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analista de Backoffice y Enlace</t>
   </si>
   <si>
     <t xml:space="preserve">Seguros Matrix</t>
   </si>
   <si>
-    <t xml:space="preserve">guarenas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coordinador(a) De Contabilidad</t>
+    <t xml:space="preserve">guatire</t>
   </si>
   <si>
     <t xml:space="preserve">Seguros Mercantil</t>
   </si>
   <si>
-    <t xml:space="preserve">guatire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coordinador(a) De Gestion Humana</t>
+    <t xml:space="preserve">los teques</t>
   </si>
   <si>
     <t xml:space="preserve">Banesco Seguros</t>
   </si>
   <si>
-    <t xml:space="preserve">los teques</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coordinador(a) De Servicios Generales</t>
+    <t xml:space="preserve">no aplica</t>
   </si>
   <si>
     <t xml:space="preserve">Seguros Occidental</t>
   </si>
   <si>
-    <t xml:space="preserve">no aplica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coordinador(a) De Soporte Tecnico</t>
-  </si>
-  <si>
     <t xml:space="preserve">Imperia</t>
   </si>
   <si>
     <t xml:space="preserve">Imperia España</t>
   </si>
   <si>
-    <t xml:space="preserve">Coordinador(a) De Calidad</t>
-  </si>
-  <si>
     <t xml:space="preserve">Portabilidad España Luz</t>
   </si>
   <si>
-    <t xml:space="preserve">Coordinador(a) De Formacion Y Calidad</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vodafone</t>
   </si>
   <si>
-    <t xml:space="preserve">Auxiliar De Vigilancia</t>
-  </si>
-  <si>
     <t xml:space="preserve">Acuba</t>
   </si>
   <si>
-    <t xml:space="preserve">Auxiliar I SSGG</t>
-  </si>
-  <si>
     <t xml:space="preserve">Telcel Mx</t>
   </si>
   <si>
-    <t xml:space="preserve">Auxiliar II SSGG</t>
-  </si>
-  <si>
     <t xml:space="preserve">Inspiring</t>
   </si>
   <si>
-    <t xml:space="preserve">Gerente De Asuntos Legales</t>
-  </si>
-  <si>
     <t xml:space="preserve">Inspiring - Medic Assist</t>
   </si>
   <si>
-    <t xml:space="preserve">Gerente De Bussiness Intelligence</t>
-  </si>
-  <si>
     <t xml:space="preserve">1000 Pagos</t>
   </si>
   <si>
-    <t xml:space="preserve">Gerente De Formacion Y Calidad</t>
-  </si>
-  <si>
     <t xml:space="preserve">1000 Pagos Ventas</t>
   </si>
   <si>
-    <t xml:space="preserve">Gerente De Gestion Humana</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cirion</t>
   </si>
   <si>
-    <t xml:space="preserve">Gerente De Ingenieria De Software</t>
-  </si>
-  <si>
     <t xml:space="preserve">Grupo Tonelli</t>
   </si>
   <si>
     <t xml:space="preserve">Cencosud</t>
   </si>
   <si>
-    <t xml:space="preserve">Gerente De Mercadeo y RRPP</t>
-  </si>
-  <si>
     <t xml:space="preserve">Coopeuch Chile</t>
   </si>
   <si>
-    <t xml:space="preserve">Gerente De Negocios</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hi4ai</t>
   </si>
   <si>
-    <t xml:space="preserve">Gerente De Administracion y Finanzas</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tecnoblue</t>
   </si>
   <si>
-    <t xml:space="preserve">Gerente De Planificacion Y Control de Gestion</t>
-  </si>
-  <si>
     <t xml:space="preserve">Spiro</t>
   </si>
   <si>
-    <t xml:space="preserve">Gerente De Servicios Generales E Infraestructura</t>
-  </si>
-  <si>
     <t xml:space="preserve">911 Mx</t>
   </si>
   <si>
-    <t xml:space="preserve">Gerente De Tecnologia Y Sistemas</t>
-  </si>
-  <si>
     <t xml:space="preserve">Iris Energia</t>
   </si>
   <si>
-    <t xml:space="preserve">Administrador(a) De Redes</t>
-  </si>
-  <si>
     <t xml:space="preserve">Global Leads</t>
   </si>
   <si>
-    <t xml:space="preserve">Asesor De Desarrollo Organizacional</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ez-Llama</t>
   </si>
   <si>
-    <t xml:space="preserve">Asistente Tecnico De Infraestructura</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hsbc – Noverite</t>
   </si>
   <si>
-    <t xml:space="preserve">Back Office</t>
-  </si>
-  <si>
     <t xml:space="preserve">Estudio Anamaya</t>
   </si>
   <si>
-    <t xml:space="preserve">Mentor Formacion Claro Chile</t>
-  </si>
-  <si>
     <t xml:space="preserve">Securitas España</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista Senior De Bussiness Intelligence</t>
-  </si>
-  <si>
     <t xml:space="preserve">Faju</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior De Calidad</t>
-  </si>
-  <si>
     <t xml:space="preserve">Distribuido</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior De Formacion</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bbva Seguros</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior De Soporte Tecnico</t>
-  </si>
-  <si>
     <t xml:space="preserve">Renoco</t>
   </si>
   <si>
     <t xml:space="preserve">Renoco Concentra</t>
   </si>
   <si>
-    <t xml:space="preserve">Supervisor De Reclutamiento Masivo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dtel Peru</t>
   </si>
   <si>
-    <t xml:space="preserve">Tecnico De Producto</t>
-  </si>
-  <si>
     <t xml:space="preserve">Templaris</t>
   </si>
   <si>
     <t xml:space="preserve">Templaris Cobranzas</t>
   </si>
   <si>
-    <t xml:space="preserve">Director de Operaciones</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bait Mx Concentra</t>
   </si>
   <si>
     <t xml:space="preserve">Bait Mx</t>
   </si>
   <si>
-    <t xml:space="preserve">Coordinador(a) de Formación</t>
-  </si>
-  <si>
     <t xml:space="preserve">Geotechnology</t>
   </si>
   <si>
-    <t xml:space="preserve">Supervisor HI4AI</t>
-  </si>
-  <si>
     <t xml:space="preserve">Liberty Express</t>
   </si>
   <si>
     <t xml:space="preserve">Liberty Express Atc</t>
   </si>
   <si>
-    <t xml:space="preserve">Team Leader</t>
-  </si>
-  <si>
     <t xml:space="preserve">Conectados Ga</t>
   </si>
   <si>
     <t xml:space="preserve">Portabilidad Conectados Chile</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior De Back office</t>
-  </si>
-  <si>
     <t xml:space="preserve">Conectados Vtr</t>
   </si>
   <si>
-    <t xml:space="preserve">Supervisor Back office</t>
-  </si>
-  <si>
     <t xml:space="preserve">1000 Pagos Atc</t>
   </si>
   <si>
-    <t xml:space="preserve">Coordinador(a) de Administranción y Finanzas</t>
-  </si>
-  <si>
     <t xml:space="preserve">Concentra Postpago Mx</t>
   </si>
   <si>
     <t xml:space="preserve">Portabilidad Postpago</t>
   </si>
   <si>
-    <t xml:space="preserve">Asistente Bussiness Intelligence</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fbm Usa</t>
   </si>
   <si>
     <t xml:space="preserve">Fbm</t>
   </si>
   <si>
-    <t xml:space="preserve">Especialista de Mercadeo y Redes Sociales</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lucy Concentra</t>
   </si>
   <si>
     <t xml:space="preserve">Lucy Ventas Mx</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista Business Intelligence 1</t>
-  </si>
-  <si>
     <t xml:space="preserve">North Market</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista Business Intelligence 2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vetsi App</t>
   </si>
   <si>
     <t xml:space="preserve">Vetsi App Ventas</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista Programador</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cashea</t>
   </si>
   <si>
     <t xml:space="preserve">Cashea Cobranzas</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista De Operaciones 1</t>
-  </si>
-  <si>
     <t xml:space="preserve">Encuestas Solvencia</t>
   </si>
   <si>
     <t xml:space="preserve">Encuestas Chile</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista De Operaciones 2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tuves</t>
   </si>
   <si>
-    <t xml:space="preserve">Especialista de Calidad</t>
-  </si>
-  <si>
     <t xml:space="preserve">Click To Call Solvencia Chile</t>
   </si>
   <si>
-    <t xml:space="preserve">Gerente de Desarrollo Organizacional y Bienestar Social</t>
-  </si>
-  <si>
     <t xml:space="preserve">Inbound Solvencia Chile</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior de Desarrollo Organizacional y Bienestar Social</t>
-  </si>
-  <si>
     <t xml:space="preserve">Outbound Bdd</t>
   </si>
   <si>
-    <t xml:space="preserve">Programador</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vtr Chile</t>
   </si>
   <si>
     <t xml:space="preserve">Vtr Movil</t>
   </si>
   <si>
-    <t xml:space="preserve">Pasante</t>
-  </si>
-  <si>
     <t xml:space="preserve">Abisun</t>
   </si>
   <si>
-    <t xml:space="preserve">Especialista Senior de Gestion Humana</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mediderm</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior de Gestión Humana</t>
-  </si>
-  <si>
     <t xml:space="preserve">Portabilidad Energia EspaÑa</t>
   </si>
   <si>
-    <t xml:space="preserve">Especialista de Gestión Humana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior de Captación y Selección de Talento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analista Contable</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ubii Pagos</t>
   </si>
   <si>
     <t xml:space="preserve">Ubii Pagos Tlv</t>
   </si>
   <si>
-    <t xml:space="preserve">Lider de Programación</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ubii Pagos Atc</t>
   </si>
   <si>
-    <t xml:space="preserve">Especialista en Creación y Gestión de Contenido Digital</t>
-  </si>
-  <si>
     <t xml:space="preserve">Excedente</t>
   </si>
   <si>
-    <t xml:space="preserve">Coordinador de Business Intelligence</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wom Chile</t>
   </si>
   <si>
-    <t xml:space="preserve">Coordinador de Planificación y Control de la Gestión</t>
-  </si>
-  <si>
     <t xml:space="preserve">Librepago</t>
   </si>
   <si>
     <t xml:space="preserve">Librepao Ventas</t>
   </si>
   <si>
-    <t xml:space="preserve"> Analista de Planificación</t>
-  </si>
-  <si>
     <t xml:space="preserve">Simpletv</t>
   </si>
   <si>
     <t xml:space="preserve">Simple Tv Reclutamiento</t>
   </si>
   <si>
-    <t xml:space="preserve">Asistente de Marketing</t>
-  </si>
-  <si>
     <t xml:space="preserve">Simple Recuperacion</t>
   </si>
   <si>
-    <t xml:space="preserve">Coordinador(a) de Desarrollo Organizacional y Bienestar Social</t>
-  </si>
-  <si>
     <t xml:space="preserve">Directv Argentina</t>
   </si>
   <si>
     <t xml:space="preserve">Directv Ventas</t>
   </si>
   <si>
-    <t xml:space="preserve">Especialista de Proyectos</t>
-  </si>
-  <si>
     <t xml:space="preserve">Renovaciones Concentra</t>
   </si>
   <si>
     <t xml:space="preserve">Renovaciones Mx</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior de Nomina</t>
-  </si>
-  <si>
     <t xml:space="preserve">Claro Costa Rica</t>
   </si>
   <si>
     <t xml:space="preserve">Claro Cr Hogar</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista de Tarifas y Precios (CANTV)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Claro Cr Pyme</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista de Investigación de Mercado (CANTV)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Upsale Mx</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista de Desarrollo de Segmentos (CANTV)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Guaupets</t>
   </si>
   <si>
     <t xml:space="preserve">Guaupets Ventas</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista de Planificación y Optimización de Procesos (CANTV)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Avicola La Guasima</t>
   </si>
   <si>
     <t xml:space="preserve">Que Pollo Atc</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Formacion y Calidad</t>
-  </si>
-  <si>
     <t xml:space="preserve">Atenas Group</t>
   </si>
   <si>
     <t xml:space="preserve">Traditional Access Cc</t>
   </si>
   <si>
-    <t xml:space="preserve">Supervisor Operativo CANTV</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ceca Porlamar Sg</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista de Redes y Datos</t>
-  </si>
-  <si>
     <t xml:space="preserve">Reina Ester</t>
   </si>
   <si>
     <t xml:space="preserve">Encuestas</t>
   </si>
   <si>
-    <t xml:space="preserve">Asistente de Marca</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kia</t>
   </si>
   <si>
     <t xml:space="preserve">Kia Encuestas</t>
   </si>
   <si>
-    <t xml:space="preserve">Ejecutivo Comercial</t>
-  </si>
-  <si>
     <t xml:space="preserve">Librepago G</t>
   </si>
   <si>
-    <t xml:space="preserve">Backoffice de Mercadeo</t>
-  </si>
-  <si>
     <t xml:space="preserve">Di Stasi Motors G</t>
   </si>
   <si>
-    <t xml:space="preserve">Asesor Comercial</t>
-  </si>
-  <si>
     <t xml:space="preserve">Corpocredit G</t>
   </si>
   <si>
-    <t xml:space="preserve">Supervisor de Ventas</t>
-  </si>
-  <si>
     <t xml:space="preserve">G-talent</t>
   </si>
   <si>
-    <t xml:space="preserve">Coordinadora de Captación y Selección de  Talentos</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ubii Pagos Cobranzas</t>
   </si>
   <si>
-    <t xml:space="preserve">Coordinador de Mercadeo y RRPP</t>
-  </si>
-  <si>
     <t xml:space="preserve">Oceanica De Seguros</t>
   </si>
   <si>
     <t xml:space="preserve">Ventas Oceanica De Seguros</t>
   </si>
   <si>
-    <t xml:space="preserve">Analista de Back Office</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cobranzas Oceanica De Seguros</t>
   </si>
   <si>
-    <t xml:space="preserve">Supervisor Senior de BackOffice</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jac Motors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bait Postpago</t>
   </si>
   <si>
     <t xml:space="preserve">Gerencia de Formacion y Calidad</t>
@@ -1600,7 +1369,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1643,6 +1412,12 @@
       <i val="true"/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Verdana"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -1736,7 +1511,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1829,6 +1604,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1909,37 +1688,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -2012,8 +1791,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AM154"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AM155"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="2.65"/>
@@ -2052,7 +1831,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="50.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="22.08"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="28.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="2" width="2.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="2" width="5.86"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="40.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="2" width="2.65"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1032" min="41" style="1" width="11.63"/>
@@ -2141,7 +1920,7 @@
       <c r="E2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="0" t="s">
         <v>24</v>
       </c>
       <c r="H2" s="9"/>
@@ -2213,7 +1992,7 @@
       <c r="E3" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="0" t="s">
         <v>41</v>
       </c>
       <c r="H3" s="9"/>
@@ -2279,7 +2058,7 @@
       <c r="E4" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="0" t="s">
         <v>57</v>
       </c>
       <c r="H4" s="9"/>
@@ -2335,7 +2114,7 @@
       <c r="E5" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="0" t="s">
         <v>69</v>
       </c>
       <c r="H5" s="10"/>
@@ -2386,7 +2165,7 @@
       <c r="E6" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="0" t="s">
         <v>79</v>
       </c>
       <c r="H6" s="10"/>
@@ -2435,7 +2214,7 @@
       <c r="E7" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="0" t="s">
         <v>88</v>
       </c>
       <c r="H7" s="10"/>
@@ -2484,7 +2263,7 @@
       <c r="E8" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="0" t="s">
         <v>97</v>
       </c>
       <c r="H8" s="10"/>
@@ -2533,7 +2312,7 @@
       <c r="E9" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="0" t="s">
         <v>106</v>
       </c>
       <c r="H9" s="10"/>
@@ -2582,7 +2361,7 @@
       <c r="E10" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="0" t="s">
         <v>114</v>
       </c>
       <c r="H10" s="10"/>
@@ -2629,7 +2408,7 @@
       <c r="E11" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="0" t="s">
         <v>122</v>
       </c>
       <c r="H11" s="10"/>
@@ -2667,7 +2446,7 @@
       <c r="E12" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" s="0" t="s">
         <v>128</v>
       </c>
       <c r="H12" s="10"/>
@@ -2704,7 +2483,7 @@
       <c r="E13" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" s="0" t="s">
         <v>134</v>
       </c>
       <c r="H13" s="10"/>
@@ -2739,7 +2518,7 @@
       <c r="E14" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" s="0" t="s">
         <v>140</v>
       </c>
       <c r="H14" s="10"/>
@@ -2774,7 +2553,7 @@
       <c r="E15" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" s="0" t="s">
         <v>146</v>
       </c>
       <c r="H15" s="10"/>
@@ -2809,7 +2588,7 @@
       <c r="E16" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="0" t="s">
         <v>152</v>
       </c>
       <c r="H16" s="10"/>
@@ -2844,7 +2623,7 @@
       <c r="E17" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="0" t="s">
         <v>157</v>
       </c>
       <c r="H17" s="10"/>
@@ -2876,7 +2655,7 @@
       <c r="E18" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" s="0" t="s">
         <v>162</v>
       </c>
       <c r="H18" s="10"/>
@@ -2908,7 +2687,7 @@
       <c r="E19" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" s="0" t="s">
         <v>167</v>
       </c>
       <c r="H19" s="10"/>
@@ -2940,7 +2719,7 @@
       <c r="E20" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G20" s="0" t="s">
         <v>173</v>
       </c>
       <c r="H20" s="10"/>
@@ -2972,7 +2751,7 @@
       <c r="E21" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" s="0" t="s">
         <v>178</v>
       </c>
       <c r="H21" s="10"/>
@@ -3004,7 +2783,7 @@
       <c r="E22" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" s="0" t="s">
         <v>183</v>
       </c>
       <c r="H22" s="10"/>
@@ -3036,7 +2815,7 @@
       <c r="E23" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" s="0" t="s">
         <v>188</v>
       </c>
       <c r="H23" s="10"/>
@@ -3068,7 +2847,7 @@
       <c r="E24" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" s="0" t="s">
         <v>193</v>
       </c>
       <c r="H24" s="10"/>
@@ -3100,7 +2879,7 @@
       <c r="E25" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" s="0" t="s">
         <v>198</v>
       </c>
       <c r="H25" s="10"/>
@@ -3128,7 +2907,7 @@
       <c r="E26" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G26" s="0" t="s">
         <v>203</v>
       </c>
       <c r="H26" s="10"/>
@@ -3153,7 +2932,7 @@
       <c r="E27" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="G27" s="0" t="s">
         <v>207</v>
       </c>
       <c r="H27" s="10"/>
@@ -3178,7 +2957,7 @@
       <c r="E28" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" s="0" t="s">
         <v>211</v>
       </c>
       <c r="H28" s="10"/>
@@ -3206,7 +2985,7 @@
       <c r="E29" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" s="0" t="s">
         <v>216</v>
       </c>
       <c r="H29" s="10"/>
@@ -3231,7 +3010,7 @@
       <c r="E30" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G30" s="0" t="s">
         <v>220</v>
       </c>
       <c r="H30" s="10"/>
@@ -3256,7 +3035,7 @@
       <c r="E31" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" s="0" t="s">
         <v>224</v>
       </c>
       <c r="H31" s="10"/>
@@ -3278,7 +3057,7 @@
       <c r="E32" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" s="0" t="s">
         <v>227</v>
       </c>
       <c r="H32" s="10"/>
@@ -3300,7 +3079,7 @@
       <c r="E33" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" s="0" t="s">
         <v>230</v>
       </c>
       <c r="H33" s="10"/>
@@ -3322,7 +3101,7 @@
       <c r="E34" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="G34" s="0" t="s">
         <v>234</v>
       </c>
       <c r="H34" s="10"/>
@@ -3344,7 +3123,7 @@
       <c r="E35" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G35" s="0" t="s">
         <v>237</v>
       </c>
       <c r="H35" s="10"/>
@@ -3366,7 +3145,7 @@
       <c r="E36" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="G36" s="0" t="s">
         <v>240</v>
       </c>
       <c r="H36" s="10"/>
@@ -3388,7 +3167,7 @@
       <c r="E37" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="G37" s="0" t="s">
         <v>243</v>
       </c>
       <c r="H37" s="10"/>
@@ -3410,7 +3189,7 @@
       <c r="E38" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="G38" s="0" t="s">
         <v>246</v>
       </c>
       <c r="H38" s="10"/>
@@ -3432,7 +3211,7 @@
       <c r="E39" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G39" s="0" t="s">
         <v>249</v>
       </c>
       <c r="H39" s="10"/>
@@ -3454,7 +3233,7 @@
       <c r="E40" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G40" s="0" t="s">
         <v>252</v>
       </c>
       <c r="H40" s="10"/>
@@ -3477,7 +3256,7 @@
       <c r="E41" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G41" s="0" t="s">
         <v>255</v>
       </c>
       <c r="H41" s="10"/>
@@ -3501,7 +3280,7 @@
       <c r="E42" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="G42" s="0" t="s">
         <v>258</v>
       </c>
       <c r="H42" s="10"/>
@@ -3525,7 +3304,7 @@
       <c r="E43" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G43" s="0" t="s">
         <v>261</v>
       </c>
       <c r="H43" s="10"/>
@@ -3549,7 +3328,7 @@
       <c r="E44" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="G44" s="0" t="s">
         <v>264</v>
       </c>
       <c r="H44" s="10"/>
@@ -3573,7 +3352,7 @@
       <c r="E45" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="G45" s="0" t="s">
         <v>267</v>
       </c>
       <c r="H45" s="10"/>
@@ -3597,7 +3376,7 @@
       <c r="E46" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="G46" s="0" t="s">
         <v>270</v>
       </c>
       <c r="H46" s="10"/>
@@ -3621,7 +3400,7 @@
       <c r="E47" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="G47" s="0" t="s">
         <v>273</v>
       </c>
       <c r="H47" s="10"/>
@@ -3645,7 +3424,7 @@
       <c r="E48" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="G48" s="0" t="s">
         <v>276</v>
       </c>
       <c r="H48" s="10"/>
@@ -3669,7 +3448,7 @@
       <c r="E49" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="G49" s="0" t="s">
         <v>279</v>
       </c>
       <c r="H49" s="10"/>
@@ -3693,7 +3472,7 @@
       <c r="E50" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="G50" s="0" t="s">
         <v>282</v>
       </c>
       <c r="H50" s="10"/>
@@ -3717,7 +3496,7 @@
       <c r="E51" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="G51" s="0" t="s">
         <v>285</v>
       </c>
       <c r="H51" s="10"/>
@@ -3741,7 +3520,7 @@
       <c r="E52" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="G52" s="1" t="s">
+      <c r="G52" s="0" t="s">
         <v>288</v>
       </c>
       <c r="H52" s="10"/>
@@ -3755,7 +3534,7 @@
         <v>51</v>
       </c>
       <c r="AJ52" s="15" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="AK52" s="15" t="s">
         <v>289</v>
@@ -3765,7 +3544,7 @@
       <c r="E53" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="G53" s="1" t="s">
+      <c r="G53" s="0" t="s">
         <v>291</v>
       </c>
       <c r="H53" s="10"/>
@@ -3789,7 +3568,7 @@
       <c r="E54" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="G54" s="1" t="s">
+      <c r="G54" s="0" t="s">
         <v>294</v>
       </c>
       <c r="H54" s="10"/>
@@ -3813,9 +3592,6 @@
       <c r="E55" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="G55" s="1" t="s">
-        <v>297</v>
-      </c>
       <c r="H55" s="10"/>
       <c r="I55" s="17"/>
       <c r="K55" s="17"/>
@@ -3827,18 +3603,15 @@
         <v>51</v>
       </c>
       <c r="AJ55" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AK55" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E56" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H56" s="10"/>
       <c r="I56" s="17"/>
@@ -3851,18 +3624,15 @@
         <v>51</v>
       </c>
       <c r="AJ56" s="15" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AK56" s="15" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E57" s="16" t="s">
-        <v>302</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H57" s="10"/>
       <c r="I57" s="17"/>
@@ -3875,16 +3645,13 @@
         <v>51</v>
       </c>
       <c r="AJ57" s="15" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="AK57" s="15" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G58" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="H58" s="10"/>
       <c r="I58" s="17"/>
       <c r="K58" s="17"/>
@@ -3896,16 +3663,13 @@
         <v>51</v>
       </c>
       <c r="AJ58" s="15" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="AK58" s="15" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G59" s="1" t="s">
-        <v>308</v>
-      </c>
       <c r="H59" s="10"/>
       <c r="I59" s="17"/>
       <c r="K59" s="17"/>
@@ -3917,16 +3681,13 @@
         <v>51</v>
       </c>
       <c r="AJ59" s="15" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="AK59" s="15" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G60" s="1" t="s">
-        <v>310</v>
-      </c>
       <c r="H60" s="10"/>
       <c r="I60" s="17"/>
       <c r="K60" s="17"/>
@@ -3938,16 +3699,13 @@
         <v>51</v>
       </c>
       <c r="AJ60" s="15" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="AK60" s="15" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G61" s="1" t="s">
-        <v>312</v>
-      </c>
       <c r="H61" s="10"/>
       <c r="I61" s="17"/>
       <c r="K61" s="17"/>
@@ -3959,16 +3717,13 @@
         <v>51</v>
       </c>
       <c r="AJ61" s="15" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="AK61" s="15" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G62" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="H62" s="10"/>
       <c r="I62" s="17"/>
       <c r="K62" s="17"/>
@@ -3980,16 +3735,13 @@
         <v>51</v>
       </c>
       <c r="AJ62" s="15" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="AK62" s="15" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G63" s="1" t="s">
-        <v>316</v>
-      </c>
       <c r="H63" s="10"/>
       <c r="I63" s="17"/>
       <c r="K63" s="17"/>
@@ -4001,16 +3753,13 @@
         <v>51</v>
       </c>
       <c r="AJ63" s="15" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="AK63" s="15" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G64" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="H64" s="10"/>
       <c r="I64" s="17"/>
       <c r="K64" s="17"/>
@@ -4022,16 +3771,13 @@
         <v>51</v>
       </c>
       <c r="AJ64" s="15" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="AK64" s="15" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G65" s="1" t="s">
-        <v>320</v>
-      </c>
       <c r="H65" s="10"/>
       <c r="I65" s="17"/>
       <c r="K65" s="17"/>
@@ -4043,16 +3789,13 @@
         <v>51</v>
       </c>
       <c r="AJ65" s="15" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="AK65" s="15" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G66" s="1" t="s">
-        <v>322</v>
-      </c>
       <c r="H66" s="10"/>
       <c r="I66" s="17"/>
       <c r="K66" s="17"/>
@@ -4064,16 +3807,13 @@
         <v>51</v>
       </c>
       <c r="AJ66" s="15" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="AK66" s="15" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G67" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="H67" s="10"/>
       <c r="I67" s="17"/>
       <c r="K67" s="17"/>
@@ -4085,16 +3825,13 @@
         <v>51</v>
       </c>
       <c r="AJ67" s="15" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="AK67" s="15" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G68" s="1" t="s">
-        <v>327</v>
-      </c>
       <c r="H68" s="10"/>
       <c r="I68" s="17"/>
       <c r="K68" s="17"/>
@@ -4106,16 +3843,13 @@
         <v>51</v>
       </c>
       <c r="AJ68" s="15" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="AK68" s="15" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G69" s="1" t="s">
-        <v>329</v>
-      </c>
       <c r="H69" s="10"/>
       <c r="I69" s="17"/>
       <c r="K69" s="17"/>
@@ -4127,16 +3861,13 @@
         <v>51</v>
       </c>
       <c r="AJ69" s="15" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="AK69" s="15" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G70" s="1" t="s">
-        <v>331</v>
-      </c>
       <c r="H70" s="10"/>
       <c r="I70" s="17"/>
       <c r="K70" s="17"/>
@@ -4148,16 +3879,13 @@
         <v>51</v>
       </c>
       <c r="AJ70" s="15" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="AK70" s="15" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G71" s="1" t="s">
-        <v>333</v>
-      </c>
       <c r="H71" s="10"/>
       <c r="I71" s="17"/>
       <c r="K71" s="17"/>
@@ -4169,16 +3897,13 @@
         <v>51</v>
       </c>
       <c r="AJ71" s="15" t="s">
-        <v>334</v>
+        <v>318</v>
       </c>
       <c r="AK71" s="15" t="s">
-        <v>334</v>
+        <v>318</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G72" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="H72" s="10"/>
       <c r="I72" s="17"/>
       <c r="K72" s="17"/>
@@ -4190,16 +3915,13 @@
         <v>51</v>
       </c>
       <c r="AJ72" s="15" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="AK72" s="15" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G73" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="H73" s="10"/>
       <c r="I73" s="17"/>
       <c r="K73" s="17"/>
@@ -4211,16 +3933,13 @@
         <v>51</v>
       </c>
       <c r="AJ73" s="15" t="s">
-        <v>338</v>
+        <v>320</v>
       </c>
       <c r="AK73" s="15" t="s">
-        <v>338</v>
+        <v>320</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G74" s="1" t="s">
-        <v>339</v>
-      </c>
       <c r="H74" s="10"/>
       <c r="I74" s="17"/>
       <c r="K74" s="17"/>
@@ -4232,16 +3951,13 @@
         <v>51</v>
       </c>
       <c r="AJ74" s="15" t="s">
-        <v>340</v>
+        <v>321</v>
       </c>
       <c r="AK74" s="15" t="s">
-        <v>340</v>
+        <v>321</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G75" s="1" t="s">
-        <v>341</v>
-      </c>
       <c r="H75" s="10"/>
       <c r="I75" s="17"/>
       <c r="K75" s="17"/>
@@ -4253,16 +3969,13 @@
         <v>51</v>
       </c>
       <c r="AJ75" s="15" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="AK75" s="15" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G76" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="H76" s="10"/>
       <c r="I76" s="17"/>
       <c r="K76" s="17"/>
@@ -4274,16 +3987,13 @@
         <v>51</v>
       </c>
       <c r="AJ76" s="15" t="s">
-        <v>344</v>
+        <v>323</v>
       </c>
       <c r="AK76" s="15" t="s">
-        <v>344</v>
+        <v>323</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G77" s="1" t="s">
-        <v>345</v>
-      </c>
       <c r="H77" s="10"/>
       <c r="I77" s="17"/>
       <c r="K77" s="17"/>
@@ -4295,16 +4005,13 @@
         <v>51</v>
       </c>
       <c r="AJ77" s="15" t="s">
-        <v>346</v>
+        <v>324</v>
       </c>
       <c r="AK77" s="15" t="s">
-        <v>346</v>
+        <v>324</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G78" s="1" t="s">
-        <v>347</v>
-      </c>
       <c r="H78" s="10"/>
       <c r="I78" s="17"/>
       <c r="K78" s="17"/>
@@ -4315,16 +4022,13 @@
         <v>51</v>
       </c>
       <c r="AJ78" s="15" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
       <c r="AK78" s="15" t="s">
-        <v>348</v>
+        <v>325</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G79" s="1" t="s">
-        <v>349</v>
-      </c>
       <c r="H79" s="10"/>
       <c r="I79" s="17"/>
       <c r="K79" s="17"/>
@@ -4335,16 +4039,13 @@
         <v>51</v>
       </c>
       <c r="AJ79" s="15" t="s">
-        <v>350</v>
+        <v>326</v>
       </c>
       <c r="AK79" s="15" t="s">
-        <v>350</v>
+        <v>326</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G80" s="1" t="s">
-        <v>351</v>
-      </c>
       <c r="H80" s="10"/>
       <c r="I80" s="17"/>
       <c r="K80" s="17"/>
@@ -4355,16 +4056,13 @@
         <v>51</v>
       </c>
       <c r="AJ80" s="15" t="s">
-        <v>352</v>
+        <v>327</v>
       </c>
       <c r="AK80" s="15" t="s">
-        <v>352</v>
+        <v>327</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G81" s="1" t="s">
-        <v>353</v>
-      </c>
       <c r="H81" s="10"/>
       <c r="I81" s="17"/>
       <c r="K81" s="17"/>
@@ -4375,16 +4073,13 @@
         <v>51</v>
       </c>
       <c r="AJ81" s="15" t="s">
-        <v>354</v>
+        <v>328</v>
       </c>
       <c r="AK81" s="15" t="s">
-        <v>354</v>
+        <v>328</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G82" s="1" t="s">
-        <v>355</v>
-      </c>
       <c r="H82" s="10"/>
       <c r="I82" s="17"/>
       <c r="K82" s="17"/>
@@ -4395,16 +4090,13 @@
         <v>51</v>
       </c>
       <c r="AJ82" s="15" t="s">
-        <v>356</v>
+        <v>329</v>
       </c>
       <c r="AK82" s="15" t="s">
-        <v>357</v>
+        <v>330</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G83" s="1" t="s">
-        <v>358</v>
-      </c>
       <c r="H83" s="10"/>
       <c r="I83" s="17"/>
       <c r="K83" s="17"/>
@@ -4415,16 +4107,13 @@
         <v>51</v>
       </c>
       <c r="AJ83" s="15" t="s">
-        <v>359</v>
+        <v>331</v>
       </c>
       <c r="AK83" s="15" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G84" s="1" t="s">
-        <v>360</v>
-      </c>
       <c r="H84" s="10"/>
       <c r="I84" s="17"/>
       <c r="K84" s="17"/>
@@ -4435,16 +4124,13 @@
         <v>51</v>
       </c>
       <c r="AJ84" s="15" t="s">
-        <v>361</v>
+        <v>332</v>
       </c>
       <c r="AK84" s="15" t="s">
-        <v>362</v>
+        <v>333</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G85" s="1" t="s">
-        <v>363</v>
-      </c>
       <c r="H85" s="10"/>
       <c r="I85" s="17"/>
       <c r="K85" s="17"/>
@@ -4455,16 +4141,13 @@
         <v>51</v>
       </c>
       <c r="AJ85" s="15" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
       <c r="AK85" s="15" t="s">
-        <v>365</v>
+        <v>335</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G86" s="1" t="s">
-        <v>366</v>
-      </c>
       <c r="H86" s="10"/>
       <c r="I86" s="17"/>
       <c r="K86" s="17"/>
@@ -4475,16 +4158,13 @@
         <v>51</v>
       </c>
       <c r="AJ86" s="15" t="s">
-        <v>367</v>
+        <v>336</v>
       </c>
       <c r="AK86" s="15" t="s">
-        <v>367</v>
+        <v>336</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G87" s="1" t="s">
-        <v>368</v>
-      </c>
       <c r="H87" s="10"/>
       <c r="I87" s="17"/>
       <c r="K87" s="17"/>
@@ -4495,16 +4175,13 @@
         <v>51</v>
       </c>
       <c r="AJ87" s="15" t="s">
-        <v>369</v>
+        <v>337</v>
       </c>
       <c r="AK87" s="15" t="s">
-        <v>370</v>
+        <v>338</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G88" s="1" t="s">
-        <v>371</v>
-      </c>
       <c r="H88" s="10"/>
       <c r="I88" s="17"/>
       <c r="K88" s="17"/>
@@ -4515,16 +4192,13 @@
         <v>51</v>
       </c>
       <c r="AJ88" s="15" t="s">
-        <v>372</v>
+        <v>339</v>
       </c>
       <c r="AK88" s="15" t="s">
-        <v>373</v>
+        <v>340</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G89" s="1" t="s">
-        <v>374</v>
-      </c>
       <c r="H89" s="10"/>
       <c r="I89" s="17"/>
       <c r="K89" s="17"/>
@@ -4537,16 +4211,13 @@
         <v>51</v>
       </c>
       <c r="AJ89" s="15" t="s">
-        <v>372</v>
+        <v>339</v>
       </c>
       <c r="AK89" s="15" t="s">
-        <v>375</v>
+        <v>341</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G90" s="1" t="s">
-        <v>376</v>
-      </c>
       <c r="H90" s="10"/>
       <c r="I90" s="17"/>
       <c r="K90" s="17"/>
@@ -4559,16 +4230,13 @@
         <v>51</v>
       </c>
       <c r="AJ90" s="15" t="s">
-        <v>377</v>
+        <v>342</v>
       </c>
       <c r="AK90" s="15" t="s">
-        <v>377</v>
+        <v>342</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G91" s="1" t="s">
-        <v>378</v>
-      </c>
       <c r="H91" s="10"/>
       <c r="I91" s="17"/>
       <c r="K91" s="17"/>
@@ -4581,16 +4249,13 @@
         <v>51</v>
       </c>
       <c r="AJ91" s="15" t="s">
-        <v>379</v>
+        <v>343</v>
       </c>
       <c r="AK91" s="15" t="s">
-        <v>380</v>
+        <v>344</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G92" s="1" t="s">
-        <v>381</v>
-      </c>
       <c r="H92" s="10"/>
       <c r="I92" s="17"/>
       <c r="K92" s="17"/>
@@ -4603,16 +4268,13 @@
         <v>51</v>
       </c>
       <c r="AJ92" s="15" t="s">
-        <v>382</v>
+        <v>345</v>
       </c>
       <c r="AK92" s="15" t="s">
-        <v>383</v>
+        <v>346</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G93" s="1" t="s">
-        <v>384</v>
-      </c>
       <c r="S93" s="21"/>
       <c r="V93" s="22"/>
       <c r="W93" s="21"/>
@@ -4620,16 +4282,13 @@
         <v>51</v>
       </c>
       <c r="AJ93" s="15" t="s">
-        <v>385</v>
+        <v>347</v>
       </c>
       <c r="AK93" s="15" t="s">
-        <v>386</v>
+        <v>348</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G94" s="1" t="s">
-        <v>387</v>
-      </c>
       <c r="S94" s="21"/>
       <c r="V94" s="22"/>
       <c r="W94" s="21"/>
@@ -4637,16 +4296,13 @@
         <v>51</v>
       </c>
       <c r="AJ94" s="15" t="s">
-        <v>388</v>
+        <v>349</v>
       </c>
       <c r="AK94" s="15" t="s">
-        <v>388</v>
+        <v>349</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G95" s="1" t="s">
-        <v>389</v>
-      </c>
       <c r="S95" s="21"/>
       <c r="V95" s="22"/>
       <c r="W95" s="21"/>
@@ -4654,16 +4310,13 @@
         <v>51</v>
       </c>
       <c r="AJ95" s="15" t="s">
-        <v>390</v>
+        <v>350</v>
       </c>
       <c r="AK95" s="15" t="s">
-        <v>391</v>
+        <v>351</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G96" s="1" t="s">
-        <v>392</v>
-      </c>
       <c r="S96" s="21"/>
       <c r="V96" s="22"/>
       <c r="W96" s="21"/>
@@ -4671,528 +4324,417 @@
         <v>51</v>
       </c>
       <c r="AJ96" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="AK96" s="15" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI97" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ97" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="AK97" s="15" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI98" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ98" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="AK98" s="15" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI99" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ99" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="AK99" s="15" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI100" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ100" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="AK100" s="15" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI101" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ101" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="AK101" s="15" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI102" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ102" s="15" t="s">
+        <v>360</v>
+      </c>
+      <c r="AK102" s="15" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI103" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ103" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="AK103" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI104" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ104" s="15" t="s">
+        <v>363</v>
+      </c>
+      <c r="AK104" s="15" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI105" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ105" s="15" t="s">
+        <v>364</v>
+      </c>
+      <c r="AK105" s="15" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI106" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ106" s="15" t="s">
+        <v>358</v>
+      </c>
+      <c r="AK106" s="15" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI107" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ107" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="AK107" s="15" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI108" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ108" s="15" t="s">
+        <v>365</v>
+      </c>
+      <c r="AK108" s="15" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI109" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ109" s="15" t="s">
+        <v>365</v>
+      </c>
+      <c r="AK109" s="15" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI110" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ110" s="15" t="s">
+        <v>368</v>
+      </c>
+      <c r="AK110" s="15" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI111" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ111" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="AK111" s="15" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI112" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ112" s="15" t="s">
+        <v>370</v>
+      </c>
+      <c r="AK112" s="15" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI113" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ113" s="15" t="s">
+        <v>372</v>
+      </c>
+      <c r="AK113" s="15" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI114" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ114" s="15" t="s">
+        <v>372</v>
+      </c>
+      <c r="AK114" s="15" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI115" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ115" s="15" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK115" s="15" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI116" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ116" s="15" t="s">
+        <v>377</v>
+      </c>
+      <c r="AK116" s="15" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI117" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ117" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="AK117" s="15" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI118" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ118" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="AK118" s="15" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI119" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ119" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="AK119" s="15" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI120" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ120" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="AK120" s="15" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI121" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ121" s="15" t="s">
+        <v>385</v>
+      </c>
+      <c r="AK121" s="15" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI122" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ122" s="15" t="s">
+        <v>387</v>
+      </c>
+      <c r="AK122" s="15" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI123" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ123" s="15" t="s">
+        <v>387</v>
+      </c>
+      <c r="AK123" s="15" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI124" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ124" s="15" t="s">
+        <v>390</v>
+      </c>
+      <c r="AK124" s="15" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI125" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ125" s="15" t="s">
+        <v>392</v>
+      </c>
+      <c r="AK125" s="15" t="s">
         <v>393</v>
       </c>
-      <c r="AK96" s="15" t="s">
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI126" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ126" s="15" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G97" s="1" t="s">
+      <c r="AK126" s="15" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI127" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ127" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="AI97" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ97" s="15" t="s">
+      <c r="AK127" s="15" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI128" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ128" s="15" t="s">
         <v>396</v>
       </c>
-      <c r="AK97" s="15" t="s">
+      <c r="AK128" s="15" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI129" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ129" s="15" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G98" s="1" t="s">
+      <c r="AK129" s="15" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI130" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ130" s="15" t="s">
         <v>398</v>
       </c>
-      <c r="AI98" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ98" s="15" t="s">
+      <c r="AK130" s="15" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI131" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ131" s="15" t="s">
         <v>399</v>
       </c>
-      <c r="AK98" s="15" t="s">
+      <c r="AK131" s="15" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI132" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ132" s="15" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G99" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="AI99" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ99" s="15" t="s">
-        <v>399</v>
-      </c>
-      <c r="AK99" s="15" t="s">
+      <c r="AK132" s="15" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G100" s="1" t="s">
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI133" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ133" s="15" t="s">
         <v>402</v>
       </c>
-      <c r="AI100" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ100" s="15" t="s">
-        <v>399</v>
-      </c>
-      <c r="AK100" s="15" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G101" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="AI101" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ101" s="15" t="s">
-        <v>399</v>
-      </c>
-      <c r="AK101" s="15" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G102" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="AI102" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ102" s="15" t="s">
-        <v>407</v>
-      </c>
-      <c r="AK102" s="15" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G103" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="AI103" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ103" s="15" t="s">
-        <v>410</v>
-      </c>
-      <c r="AK103" s="15" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G104" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="AI104" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ104" s="15" t="s">
-        <v>412</v>
-      </c>
-      <c r="AK104" s="15" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G105" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="AI105" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ105" s="15" t="s">
-        <v>414</v>
-      </c>
-      <c r="AK105" s="15" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G106" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="AI106" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ106" s="15" t="s">
-        <v>403</v>
-      </c>
-      <c r="AK106" s="15" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G107" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="AI107" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ107" s="15" t="s">
-        <v>401</v>
-      </c>
-      <c r="AK107" s="15" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G108" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="AI108" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ108" s="15" t="s">
-        <v>418</v>
-      </c>
-      <c r="AK108" s="15" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G109" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="AI109" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ109" s="15" t="s">
-        <v>418</v>
-      </c>
-      <c r="AK109" s="15" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G110" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="AI110" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ110" s="15" t="s">
-        <v>423</v>
-      </c>
-      <c r="AK110" s="15" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G111" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="AI111" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ111" s="15" t="s">
-        <v>425</v>
-      </c>
-      <c r="AK111" s="15" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G112" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="AI112" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ112" s="15" t="s">
-        <v>427</v>
-      </c>
-      <c r="AK112" s="15" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G113" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="AI113" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ113" s="15" t="s">
-        <v>430</v>
-      </c>
-      <c r="AK113" s="15" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G114" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="AI114" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ114" s="15" t="s">
-        <v>430</v>
-      </c>
-      <c r="AK114" s="15" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G115" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="AI115" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ115" s="15" t="s">
-        <v>435</v>
-      </c>
-      <c r="AK115" s="15" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G116" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="AI116" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ116" s="15" t="s">
-        <v>438</v>
-      </c>
-      <c r="AK116" s="15" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G117" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="AI117" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ117" s="15" t="s">
-        <v>441</v>
-      </c>
-      <c r="AK117" s="15" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G118" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="AI118" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ118" s="15" t="s">
-        <v>441</v>
-      </c>
-      <c r="AK118" s="15" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G119" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="AI119" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ119" s="15" t="s">
-        <v>446</v>
-      </c>
-      <c r="AK119" s="15" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G120" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="AI120" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ120" s="15" t="s">
-        <v>448</v>
-      </c>
-      <c r="AK120" s="15" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G121" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="AI121" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ121" s="15" t="s">
-        <v>451</v>
-      </c>
-      <c r="AK121" s="15" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G122" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="AI122" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ122" s="15" t="s">
-        <v>454</v>
-      </c>
-      <c r="AK122" s="15" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G123" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="AI123" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ123" s="15" t="s">
-        <v>454</v>
-      </c>
-      <c r="AK123" s="15" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G124" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="AI124" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ124" s="15" t="s">
-        <v>459</v>
-      </c>
-      <c r="AK124" s="15" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G125" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="AI125" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ125" s="15" t="s">
-        <v>462</v>
-      </c>
-      <c r="AK125" s="15" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G126" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="AI126" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ126" s="15" t="s">
-        <v>465</v>
-      </c>
-      <c r="AK126" s="15" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G127" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="AI127" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ127" s="15" t="s">
-        <v>467</v>
-      </c>
-      <c r="AK127" s="15" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G128" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="AI128" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ128" s="15" t="s">
-        <v>469</v>
-      </c>
-      <c r="AK128" s="15" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G129" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="AI129" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ129" s="15" t="s">
-        <v>471</v>
-      </c>
-      <c r="AK129" s="15" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G130" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="AI130" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ130" s="15" t="s">
-        <v>473</v>
-      </c>
-      <c r="AK130" s="15" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G131" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="AI131" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ131" s="15" t="s">
-        <v>475</v>
-      </c>
-      <c r="AK131" s="15" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G132" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="AI132" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ132" s="15" t="s">
-        <v>475</v>
-      </c>
-      <c r="AK132" s="15" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G133" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="AI133" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ133" s="15" t="s">
-        <v>480</v>
-      </c>
       <c r="AK133" s="15" t="s">
-        <v>480</v>
+        <v>402</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5200,136 +4742,136 @@
         <v>51</v>
       </c>
       <c r="AJ134" s="15" t="s">
-        <v>480</v>
+        <v>402</v>
       </c>
       <c r="AK134" s="15" t="s">
-        <v>480</v>
+        <v>402</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI135" s="15" t="s">
-        <v>481</v>
+        <v>51</v>
       </c>
       <c r="AJ135" s="15" t="s">
-        <v>36</v>
+        <v>403</v>
       </c>
       <c r="AK135" s="15" t="s">
-        <v>482</v>
+        <v>403</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI136" s="15" t="s">
-        <v>481</v>
+        <v>404</v>
       </c>
       <c r="AJ136" s="15" t="s">
         <v>36</v>
       </c>
       <c r="AK136" s="15" t="s">
-        <v>483</v>
+        <v>405</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI137" s="15" t="s">
-        <v>481</v>
+        <v>404</v>
       </c>
       <c r="AJ137" s="15" t="s">
         <v>36</v>
       </c>
       <c r="AK137" s="15" t="s">
-        <v>484</v>
+        <v>406</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI138" s="15" t="s">
-        <v>481</v>
+        <v>404</v>
       </c>
       <c r="AJ138" s="15" t="s">
         <v>36</v>
       </c>
       <c r="AK138" s="15" t="s">
-        <v>352</v>
+        <v>407</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI139" s="15" t="s">
-        <v>485</v>
+        <v>404</v>
       </c>
       <c r="AJ139" s="15" t="s">
         <v>36</v>
       </c>
       <c r="AK139" s="15" t="s">
-        <v>36</v>
+        <v>327</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI140" s="15" t="s">
-        <v>485</v>
+        <v>408</v>
       </c>
       <c r="AJ140" s="15" t="s">
         <v>36</v>
       </c>
       <c r="AK140" s="15" t="s">
-        <v>352</v>
+        <v>36</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI141" s="15" t="s">
-        <v>485</v>
+        <v>408</v>
       </c>
       <c r="AJ141" s="15" t="s">
-        <v>486</v>
+        <v>36</v>
       </c>
       <c r="AK141" s="15" t="s">
-        <v>487</v>
+        <v>327</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI142" s="15" t="s">
-        <v>485</v>
+        <v>408</v>
       </c>
       <c r="AJ142" s="15" t="s">
-        <v>488</v>
+        <v>409</v>
       </c>
       <c r="AK142" s="15" t="s">
-        <v>488</v>
+        <v>410</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI143" s="15" t="s">
-        <v>489</v>
+        <v>408</v>
       </c>
       <c r="AJ143" s="15" t="s">
-        <v>36</v>
+        <v>411</v>
       </c>
       <c r="AK143" s="15" t="s">
-        <v>36</v>
+        <v>411</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI144" s="15" t="s">
-        <v>489</v>
+        <v>412</v>
       </c>
       <c r="AJ144" s="15" t="s">
         <v>36</v>
       </c>
       <c r="AK144" s="15" t="s">
-        <v>352</v>
+        <v>36</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI145" s="15" t="s">
-        <v>490</v>
+        <v>412</v>
       </c>
       <c r="AJ145" s="15" t="s">
         <v>36</v>
       </c>
       <c r="AK145" s="15" t="s">
-        <v>36</v>
+        <v>327</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI146" s="15" t="s">
-        <v>491</v>
+        <v>413</v>
       </c>
       <c r="AJ146" s="15" t="s">
         <v>36</v>
@@ -5340,7 +4882,7 @@
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI147" s="15" t="s">
-        <v>492</v>
+        <v>414</v>
       </c>
       <c r="AJ147" s="15" t="s">
         <v>36</v>
@@ -5351,7 +4893,7 @@
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI148" s="15" t="s">
-        <v>493</v>
+        <v>415</v>
       </c>
       <c r="AJ148" s="15" t="s">
         <v>36</v>
@@ -5362,7 +4904,7 @@
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI149" s="15" t="s">
-        <v>494</v>
+        <v>416</v>
       </c>
       <c r="AJ149" s="15" t="s">
         <v>36</v>
@@ -5373,7 +4915,7 @@
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI150" s="15" t="s">
-        <v>495</v>
+        <v>417</v>
       </c>
       <c r="AJ150" s="15" t="s">
         <v>36</v>
@@ -5384,7 +4926,7 @@
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI151" s="15" t="s">
-        <v>496</v>
+        <v>418</v>
       </c>
       <c r="AJ151" s="15" t="s">
         <v>36</v>
@@ -5395,7 +4937,7 @@
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI152" s="15" t="s">
-        <v>497</v>
+        <v>419</v>
       </c>
       <c r="AJ152" s="15" t="s">
         <v>36</v>
@@ -5406,7 +4948,7 @@
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI153" s="15" t="s">
-        <v>498</v>
+        <v>420</v>
       </c>
       <c r="AJ153" s="15" t="s">
         <v>36</v>
@@ -5417,12 +4959,23 @@
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI154" s="15" t="s">
-        <v>499</v>
+        <v>421</v>
       </c>
       <c r="AJ154" s="15" t="s">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AK154" s="15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AI155" s="23" t="s">
+        <v>422</v>
+      </c>
+      <c r="AJ155" s="23" t="s">
+        <v>423</v>
+      </c>
+      <c r="AK155" s="23" t="s">
         <v>36</v>
       </c>
     </row>
@@ -5445,17 +4998,29 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:K53"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>501</v>
+        <v>424</v>
       </c>
       <c r="D1" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="J1" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5464,9 +5029,21 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>502</v>
+        <v>425</v>
       </c>
       <c r="D2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="J2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5475,9 +5052,21 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>503</v>
+        <v>426</v>
       </c>
       <c r="D3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="J3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5486,9 +5075,21 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>504</v>
+        <v>427</v>
       </c>
       <c r="D4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5497,9 +5098,21 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>505</v>
+        <v>428</v>
       </c>
       <c r="D5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5508,9 +5121,21 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>506</v>
+        <v>429</v>
       </c>
       <c r="D6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="J6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5519,9 +5144,21 @@
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>507</v>
+        <v>430</v>
       </c>
       <c r="D7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="J7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5530,9 +5167,21 @@
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>501</v>
+        <v>424</v>
       </c>
       <c r="D8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="I8" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5541,9 +5190,21 @@
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>508</v>
+        <v>431</v>
       </c>
       <c r="D9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="I9" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5552,9 +5213,21 @@
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>509</v>
+        <v>432</v>
       </c>
       <c r="D10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="I10" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="J10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5563,9 +5236,21 @@
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>510</v>
+        <v>433</v>
       </c>
       <c r="D11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5574,9 +5259,21 @@
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>511</v>
+        <v>434</v>
       </c>
       <c r="D12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="I12" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="J12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5585,9 +5282,21 @@
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>512</v>
+        <v>435</v>
       </c>
       <c r="D13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="I13" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="J13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5596,9 +5305,21 @@
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>513</v>
+        <v>436</v>
       </c>
       <c r="D14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="I14" s="0" t="s">
+        <v>146</v>
+      </c>
+      <c r="J14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5607,9 +5328,21 @@
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>513</v>
+        <v>436</v>
       </c>
       <c r="D15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="I15" s="0" t="s">
+        <v>152</v>
+      </c>
+      <c r="J15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5618,9 +5351,21 @@
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>514</v>
+        <v>437</v>
       </c>
       <c r="D16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="I16" s="0" t="s">
+        <v>157</v>
+      </c>
+      <c r="J16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5629,9 +5374,21 @@
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>515</v>
+        <v>438</v>
       </c>
       <c r="D17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="I17" s="0" t="s">
+        <v>162</v>
+      </c>
+      <c r="J17" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5640,9 +5397,21 @@
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>516</v>
+        <v>439</v>
       </c>
       <c r="D18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="I18" s="0" t="s">
+        <v>167</v>
+      </c>
+      <c r="J18" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5651,9 +5420,21 @@
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>517</v>
+        <v>440</v>
       </c>
       <c r="D19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="I19" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="J19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5662,9 +5443,21 @@
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>518</v>
+        <v>441</v>
       </c>
       <c r="D20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="I20" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="J20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5673,9 +5466,21 @@
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>519</v>
+        <v>442</v>
       </c>
       <c r="D21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="I21" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="J21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5684,9 +5489,21 @@
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>520</v>
+        <v>443</v>
       </c>
       <c r="D22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="0" t="n">
+        <v>44</v>
+      </c>
+      <c r="I22" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="J22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5695,9 +5512,21 @@
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>521</v>
+        <v>444</v>
       </c>
       <c r="D23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="I23" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="J23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5706,9 +5535,427 @@
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>522</v>
+        <v>445</v>
       </c>
       <c r="D24" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="0" t="n">
+        <v>49</v>
+      </c>
+      <c r="I24" s="0" t="s">
+        <v>198</v>
+      </c>
+      <c r="J24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H25" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="I25" s="0" t="s">
+        <v>203</v>
+      </c>
+      <c r="J25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H26" s="0" t="n">
+        <v>51</v>
+      </c>
+      <c r="I26" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="J26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H27" s="0" t="n">
+        <v>55</v>
+      </c>
+      <c r="I27" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="J27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H28" s="0" t="n">
+        <v>59</v>
+      </c>
+      <c r="I28" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="J28" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H29" s="0" t="n">
+        <v>66</v>
+      </c>
+      <c r="I29" s="0" t="s">
+        <v>220</v>
+      </c>
+      <c r="J29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H30" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="I30" s="0" t="s">
+        <v>224</v>
+      </c>
+      <c r="J30" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H31" s="0" t="n">
+        <v>69</v>
+      </c>
+      <c r="I31" s="0" t="s">
+        <v>227</v>
+      </c>
+      <c r="J31" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H32" s="0" t="n">
+        <v>71</v>
+      </c>
+      <c r="I32" s="0" t="s">
+        <v>230</v>
+      </c>
+      <c r="J32" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H33" s="0" t="n">
+        <v>73</v>
+      </c>
+      <c r="I33" s="0" t="s">
+        <v>234</v>
+      </c>
+      <c r="J33" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H34" s="0" t="n">
+        <v>74</v>
+      </c>
+      <c r="I34" s="0" t="s">
+        <v>237</v>
+      </c>
+      <c r="J34" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H35" s="0" t="n">
+        <v>75</v>
+      </c>
+      <c r="I35" s="0" t="s">
+        <v>240</v>
+      </c>
+      <c r="J35" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H36" s="0" t="n">
+        <v>76</v>
+      </c>
+      <c r="I36" s="0" t="s">
+        <v>243</v>
+      </c>
+      <c r="J36" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H37" s="0" t="n">
+        <v>82</v>
+      </c>
+      <c r="I37" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="J37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H38" s="0" t="n">
+        <v>84</v>
+      </c>
+      <c r="I38" s="0" t="s">
+        <v>249</v>
+      </c>
+      <c r="J38" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H39" s="0" t="n">
+        <v>87</v>
+      </c>
+      <c r="I39" s="0" t="s">
+        <v>252</v>
+      </c>
+      <c r="J39" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H40" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="I40" s="0" t="s">
+        <v>255</v>
+      </c>
+      <c r="J40" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H41" s="0" t="n">
+        <v>106</v>
+      </c>
+      <c r="I41" s="0" t="s">
+        <v>258</v>
+      </c>
+      <c r="J41" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H42" s="0" t="n">
+        <v>107</v>
+      </c>
+      <c r="I42" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="J42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H43" s="0" t="n">
+        <v>111</v>
+      </c>
+      <c r="I43" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="J43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H44" s="0" t="n">
+        <v>112</v>
+      </c>
+      <c r="I44" s="0" t="s">
+        <v>267</v>
+      </c>
+      <c r="J44" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H45" s="0" t="n">
+        <v>114</v>
+      </c>
+      <c r="I45" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="J45" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H46" s="0" t="n">
+        <v>116</v>
+      </c>
+      <c r="I46" s="0" t="s">
+        <v>273</v>
+      </c>
+      <c r="J46" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H47" s="0" t="n">
+        <v>117</v>
+      </c>
+      <c r="I47" s="0" t="s">
+        <v>276</v>
+      </c>
+      <c r="J47" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H48" s="0" t="n">
+        <v>122</v>
+      </c>
+      <c r="I48" s="0" t="s">
+        <v>279</v>
+      </c>
+      <c r="J48" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H49" s="0" t="n">
+        <v>135</v>
+      </c>
+      <c r="I49" s="0" t="s">
+        <v>282</v>
+      </c>
+      <c r="J49" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H50" s="0" t="n">
+        <v>136</v>
+      </c>
+      <c r="I50" s="0" t="s">
+        <v>285</v>
+      </c>
+      <c r="J50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H51" s="0" t="n">
+        <v>138</v>
+      </c>
+      <c r="I51" s="0" t="s">
+        <v>288</v>
+      </c>
+      <c r="J51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H52" s="0" t="n">
+        <v>139</v>
+      </c>
+      <c r="I52" s="0" t="s">
+        <v>291</v>
+      </c>
+      <c r="J52" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H53" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="I53" s="0" t="s">
+        <v>294</v>
+      </c>
+      <c r="J53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="0" t="n">
         <v>1</v>
       </c>
     </row>
